--- a/exciton.xlsx
+++ b/exciton.xlsx
@@ -136,7 +136,7 @@
       <family val="0"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -159,6 +159,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor rgb="FF993300"/>
       </patternFill>
     </fill>
   </fills>
@@ -196,7 +202,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -221,19 +227,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -315,7 +317,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AJ23"/>
-  <sheetFormatPr defaultColWidth="11.83984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.859375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -1636,7 +1638,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AE18"/>
-  <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.7421875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
@@ -2712,7 +2714,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AB20"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
@@ -2782,7 +2784,7 @@
       <c r="N3" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="P3" s="0" t="n">
+      <c r="P3" s="2" t="n">
         <v>2</v>
       </c>
       <c r="Q3" s="2" t="n">
@@ -2823,29 +2825,23 @@
       <c r="C4" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
       <c r="J4" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="K4" s="7"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="7"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
       <c r="Q4" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="R4" s="7"/>
-      <c r="S4" s="6"/>
-      <c r="T4" s="6"/>
-      <c r="U4" s="7"/>
+      <c r="S4" s="4"/>
+      <c r="T4" s="4"/>
       <c r="X4" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="Y4" s="7"/>
-      <c r="Z4" s="6"/>
-      <c r="AA4" s="6"/>
-      <c r="AB4" s="7"/>
+      <c r="Z4" s="4"/>
+      <c r="AA4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C5" s="0" t="n">
@@ -2854,10 +2850,10 @@
       <c r="D5" s="0" t="n">
         <v>0.4828</v>
       </c>
-      <c r="E5" s="8" t="n">
+      <c r="E5" s="6" t="n">
         <v>1.8094</v>
       </c>
-      <c r="F5" s="8" t="n">
+      <c r="F5" s="6" t="n">
         <v>1.8094</v>
       </c>
       <c r="G5" s="0" t="n">
@@ -2873,10 +2869,10 @@
       <c r="K5" s="0" t="n">
         <v>0.4828</v>
       </c>
-      <c r="L5" s="8" t="n">
+      <c r="L5" s="6" t="n">
         <v>1.8094</v>
       </c>
-      <c r="M5" s="8" t="n">
+      <c r="M5" s="6" t="n">
         <v>1.8094</v>
       </c>
       <c r="N5" s="0" t="n">
@@ -2892,10 +2888,10 @@
       <c r="R5" s="0" t="n">
         <v>0.4828</v>
       </c>
-      <c r="S5" s="8" t="n">
+      <c r="S5" s="6" t="n">
         <v>1.8094</v>
       </c>
-      <c r="T5" s="8" t="n">
+      <c r="T5" s="6" t="n">
         <v>1.8094</v>
       </c>
       <c r="U5" s="0" t="n">
@@ -2911,10 +2907,10 @@
       <c r="Y5" s="0" t="n">
         <v>0.4828</v>
       </c>
-      <c r="Z5" s="8" t="n">
+      <c r="Z5" s="6" t="n">
         <v>1.8094</v>
       </c>
-      <c r="AA5" s="8" t="n">
+      <c r="AA5" s="6" t="n">
         <v>1.8094</v>
       </c>
       <c r="AB5" s="0" t="n">
@@ -3107,23 +3103,44 @@
         <v>1.0068</v>
       </c>
     </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P9" s="0" t="n">
+        <f aca="false">COS(3.14159265359/(Q9+1))</f>
+        <v>0.866025403784421</v>
+      </c>
+      <c r="Q9" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="R9" s="0" t="n">
+        <v>1.0974</v>
+      </c>
+      <c r="S9" s="0" t="n">
+        <v>1.8383</v>
+      </c>
+      <c r="T9" s="0" t="n">
+        <v>1.9399</v>
+      </c>
+      <c r="U9" s="0" t="n">
+        <v>1.1062</v>
+      </c>
+    </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L10" s="9" t="n">
+      <c r="L10" s="7" t="n">
         <v>1.8776</v>
       </c>
-      <c r="M10" s="9" t="n">
+      <c r="M10" s="7" t="n">
         <v>1.9444</v>
       </c>
-      <c r="S10" s="9" t="n">
+      <c r="S10" s="8" t="n">
         <v>1.84</v>
       </c>
-      <c r="T10" s="9" t="n">
+      <c r="T10" s="8" t="n">
         <v>1.9554</v>
       </c>
-      <c r="Z10" s="9" t="n">
+      <c r="Z10" s="7" t="n">
         <v>1.8111</v>
       </c>
-      <c r="AA10" s="9" t="n">
+      <c r="AA10" s="7" t="n">
         <v>1.9684</v>
       </c>
     </row>
@@ -3172,16 +3189,20 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="0" t="n">
+        <f aca="false">COS(3.14159265359/(C16+1))</f>
+        <v>-1.03411553555107E-013</v>
+      </c>
       <c r="C16" s="0" t="n">
         <v>1</v>
       </c>
       <c r="D16" s="0" t="n">
         <v>0.4828</v>
       </c>
-      <c r="E16" s="8" t="n">
+      <c r="E16" s="6" t="n">
         <v>1.8094</v>
       </c>
-      <c r="F16" s="8" t="n">
+      <c r="F16" s="6" t="n">
         <v>1.8094</v>
       </c>
       <c r="G16" s="0" t="n">
@@ -3189,6 +3210,10 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="0" t="n">
+        <f aca="false">COS(3.14159265359/(C17+1))</f>
+        <v>0.49999999999994</v>
+      </c>
       <c r="C17" s="0" t="n">
         <v>2</v>
       </c>
@@ -3206,6 +3231,10 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="0" t="n">
+        <f aca="false">COS(3.14159265359/(C18+1))</f>
+        <v>0.707106781186511</v>
+      </c>
       <c r="C18" s="0" t="n">
         <v>3</v>
       </c>
@@ -3223,6 +3252,10 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="0" t="n">
+        <f aca="false">COS(3.14159265359/(C19+1))</f>
+        <v>0.809016994374923</v>
+      </c>
       <c r="C19" s="0" t="n">
         <v>4</v>
       </c>
@@ -3240,6 +3273,10 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="0" t="n">
+        <f aca="false">COS(3.14159265359/(C20+1))</f>
+        <v>0.866025403784421</v>
+      </c>
       <c r="C20" s="0" t="n">
         <v>5</v>
       </c>

--- a/exciton.xlsx
+++ b/exciton.xlsx
@@ -317,7 +317,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AJ23"/>
-  <sheetFormatPr defaultColWidth="11.859375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -1624,7 +1624,7 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Обычный"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Обычный"&amp;12Страница &amp;P</oddFooter>
@@ -1638,7 +1638,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AE18"/>
-  <sheetFormatPr defaultColWidth="11.7421875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.7578125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
@@ -2700,7 +2700,7 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Обычный"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Обычный"&amp;12Страница &amp;P</oddFooter>
@@ -2713,8 +2713,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AB20"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:AB21"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
@@ -3293,10 +3293,18 @@
         <v>1.1878</v>
       </c>
     </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E21" s="7" t="n">
+        <v>1.7239</v>
+      </c>
+      <c r="F21" s="7" t="n">
+        <v>1.97</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Обычный"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Обычный"&amp;12Страница &amp;P</oddFooter>

--- a/exciton.xlsx
+++ b/exciton.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="27">
   <si>
     <t xml:space="preserve">along N-Zn-N</t>
   </si>
@@ -109,9 +109,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="0.00"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -202,7 +203,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -236,6 +237,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -317,7 +322,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AJ23"/>
-  <sheetFormatPr defaultColWidth="11.875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.89453125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -1638,7 +1643,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AE18"/>
-  <sheetFormatPr defaultColWidth="11.7578125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.77734375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
@@ -2714,7 +2719,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AB21"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
@@ -3171,6 +3176,12 @@
       <c r="G13" s="0" t="s">
         <v>26</v>
       </c>
+      <c r="P13" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q13" s="0" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="n">
@@ -3182,11 +3193,34 @@
       <c r="C14" s="0" t="n">
         <v>3.214</v>
       </c>
+      <c r="P14" s="2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q14" s="9" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="S14" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="T14" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="U14" s="0" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C15" s="0" t="s">
         <v>19</v>
       </c>
+      <c r="Q15" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="S15" s="4"/>
+      <c r="T15" s="4"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="0" t="n">
@@ -3208,6 +3242,25 @@
       <c r="G16" s="0" t="n">
         <v>0.4828</v>
       </c>
+      <c r="P16" s="0" t="n">
+        <f aca="false">COS(3.14159265359/(Q16+1))</f>
+        <v>-1.03411553555107E-013</v>
+      </c>
+      <c r="Q16" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" s="0" t="n">
+        <v>0.4828</v>
+      </c>
+      <c r="S16" s="6" t="n">
+        <v>1.8094</v>
+      </c>
+      <c r="T16" s="6" t="n">
+        <v>1.8094</v>
+      </c>
+      <c r="U16" s="0" t="n">
+        <v>0.4828</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="0" t="n">
@@ -3229,6 +3282,25 @@
       <c r="G17" s="0" t="n">
         <v>0.6963</v>
       </c>
+      <c r="P17" s="0" t="n">
+        <f aca="false">COS(3.14159265359/(Q17+1))</f>
+        <v>0.49999999999994</v>
+      </c>
+      <c r="Q17" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="R17" s="0" t="n">
+        <v>0.5833</v>
+      </c>
+      <c r="S17" s="0" t="n">
+        <v>1.7973</v>
+      </c>
+      <c r="T17" s="0" t="n">
+        <v>1.8666</v>
+      </c>
+      <c r="U17" s="0" t="n">
+        <v>0.632</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="0" t="n">
@@ -3250,6 +3322,25 @@
       <c r="G18" s="0" t="n">
         <v>0.8711</v>
       </c>
+      <c r="P18" s="0" t="n">
+        <f aca="false">COS(3.14159265359/(Q18+1))</f>
+        <v>0.707106781186511</v>
+      </c>
+      <c r="Q18" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="R18" s="0" t="n">
+        <v>0.7073</v>
+      </c>
+      <c r="S18" s="0" t="n">
+        <v>1.7996</v>
+      </c>
+      <c r="T18" s="0" t="n">
+        <v>1.8919</v>
+      </c>
+      <c r="U18" s="0" t="n">
+        <v>0.762</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="0" t="n">
@@ -3270,6 +3361,25 @@
       </c>
       <c r="G19" s="0" t="n">
         <v>1.0328</v>
+      </c>
+      <c r="P19" s="0" t="n">
+        <f aca="false">COS(3.14159265359/(Q19+1))</f>
+        <v>0.809016994374923</v>
+      </c>
+      <c r="Q19" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="R19" s="0" t="n">
+        <v>0.8389</v>
+      </c>
+      <c r="S19" s="0" t="n">
+        <v>1.801</v>
+      </c>
+      <c r="T19" s="0" t="n">
+        <v>1.9289</v>
+      </c>
+      <c r="U19" s="0" t="n">
+        <v>0.8875</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/exciton.xlsx
+++ b/exciton.xlsx
@@ -8,9 +8,9 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="Лист1" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="Лист2" sheetId="2" state="visible" r:id="rId3"/>
-    <sheet name="Лист3" sheetId="3" state="visible" r:id="rId4"/>
+    <sheet name="Лист1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Лист2" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Лист3" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="28">
   <si>
     <t xml:space="preserve">along N-Zn-N</t>
   </si>
@@ -103,6 +103,9 @@
   </si>
   <si>
     <t xml:space="preserve">f2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(N = 2...4)</t>
   </si>
 </sst>
 </file>
@@ -203,32 +206,48 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -240,7 +259,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -316,8 +335,114 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="LibreOffice">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="ffffff"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="ffffff"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="18a303"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="0369a3"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="a33e03"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8e03a3"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="c99c00"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="c9211e"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000ee"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="551a8b"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -330,25 +455,25 @@
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
-      <c r="D1" s="0"/>
-      <c r="E1" s="0"/>
-      <c r="F1" s="0"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="0"/>
-      <c r="J1" s="0"/>
-      <c r="K1" s="0"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
-      <c r="N1" s="0"/>
-      <c r="O1" s="0"/>
-      <c r="P1" s="0"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
       <c r="Q1" s="2"/>
-      <c r="S1" s="0"/>
-      <c r="T1" s="0"/>
-      <c r="U1" s="0"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="3"/>
+      <c r="U1" s="3"/>
       <c r="V1" s="2"/>
-      <c r="X1" s="0"/>
+      <c r="X1" s="3"/>
     </row>
     <row r="2" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
@@ -360,47 +485,47 @@
       <c r="C2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>2</v>
       </c>
       <c r="H2" s="2"/>
-      <c r="I2" s="0"/>
-      <c r="J2" s="0"/>
-      <c r="K2" s="0"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
       <c r="L2" s="2" t="n">
         <v>3.5</v>
       </c>
       <c r="M2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="N2" s="0" t="s">
+      <c r="N2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="O2" s="0" t="s">
+      <c r="O2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="P2" s="0" t="s">
+      <c r="P2" s="3" t="s">
         <v>7</v>
       </c>
       <c r="Q2" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="S2" s="0"/>
-      <c r="T2" s="0"/>
-      <c r="U2" s="0"/>
+      <c r="S2" s="3"/>
+      <c r="T2" s="3"/>
+      <c r="U2" s="3"/>
       <c r="V2" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="X2" s="0"/>
+      <c r="X2" s="3"/>
       <c r="AA2" s="1" t="n">
         <v>6</v>
       </c>
@@ -409,1227 +534,1227 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="F3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="0" t="s">
+      <c r="G3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="0" t="s">
+      <c r="H3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="K3" s="0" t="s">
+      <c r="K3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L3" s="0" t="s">
+      <c r="L3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="0" t="s">
+      <c r="M3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="N3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="O3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="P3" s="0" t="s">
+      <c r="P3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="Q3" s="0" t="s">
+      <c r="Q3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="R3" s="0" t="s">
+      <c r="R3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S3" s="3" t="s">
+      <c r="S3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="T3" s="3" t="s">
+      <c r="T3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="U3" s="0" t="s">
+      <c r="U3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="V3" s="4" t="s">
+      <c r="V3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="W3" s="0" t="s">
+      <c r="W3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X3" s="3" t="s">
+      <c r="X3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="Y3" s="3" t="s">
+      <c r="Y3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="Z3" s="0" t="s">
+      <c r="Z3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="AA3" s="4" t="s">
+      <c r="AA3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="AB3" s="4" t="s">
+      <c r="AB3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="AC3" s="3" t="s">
+      <c r="AC3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="AD3" s="3" t="s">
+      <c r="AD3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="AE3" s="4" t="s">
+      <c r="AE3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="AF3" s="4" t="s">
+      <c r="AF3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="AG3" s="4" t="s">
+      <c r="AG3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="AH3" s="3" t="s">
+      <c r="AH3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="AI3" s="3" t="s">
+      <c r="AI3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="AJ3" s="4" t="s">
+      <c r="AJ3" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="6" t="n">
         <v>1.8094</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="C4" s="0" t="n">
+      <c r="C4" s="3" t="n">
         <v>1.8051</v>
       </c>
-      <c r="D4" s="0" t="n">
+      <c r="D4" s="3" t="n">
         <v>1.8336</v>
       </c>
-      <c r="E4" s="0" t="n">
+      <c r="E4" s="3" t="n">
         <v>1.77</v>
       </c>
-      <c r="F4" s="0" t="n">
+      <c r="F4" s="3" t="n">
         <v>1.8187</v>
       </c>
-      <c r="G4" s="0" t="n">
+      <c r="G4" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="H4" s="0" t="n">
+      <c r="H4" s="3" t="n">
         <v>1.804</v>
       </c>
-      <c r="I4" s="0" t="n">
+      <c r="I4" s="3" t="n">
         <v>1.8319</v>
       </c>
-      <c r="J4" s="0" t="n">
+      <c r="J4" s="3" t="n">
         <v>1.7759</v>
       </c>
-      <c r="K4" s="0" t="n">
+      <c r="K4" s="3" t="n">
         <v>1.8175</v>
       </c>
-      <c r="L4" s="0" t="n">
+      <c r="L4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M4" s="0" t="n">
+      <c r="M4" s="3" t="n">
         <v>1.1471</v>
       </c>
-      <c r="N4" s="0" t="n">
+      <c r="N4" s="3" t="n">
         <v>1.1471</v>
       </c>
-      <c r="O4" s="0" t="n">
+      <c r="O4" s="3" t="n">
         <v>1.9135</v>
       </c>
-      <c r="P4" s="0" t="n">
+      <c r="P4" s="3" t="n">
         <v>1.9135</v>
       </c>
-      <c r="Q4" s="0" t="n">
+      <c r="Q4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="R4" s="0" t="n">
+      <c r="R4" s="3" t="n">
         <v>1.5195</v>
       </c>
-      <c r="S4" s="0" t="n">
+      <c r="S4" s="3" t="n">
         <v>1.5195</v>
       </c>
-      <c r="T4" s="0" t="n">
+      <c r="T4" s="3" t="n">
         <v>1.8998</v>
       </c>
-      <c r="U4" s="0" t="n">
+      <c r="U4" s="3" t="n">
         <v>1.8998</v>
       </c>
-      <c r="V4" s="4" t="n">
+      <c r="V4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="W4" s="0" t="n">
+      <c r="W4" s="3" t="n">
         <v>1.6913</v>
       </c>
-      <c r="X4" s="4" t="n">
+      <c r="X4" s="5" t="n">
         <v>1.6913</v>
       </c>
-      <c r="Y4" s="0" t="n">
+      <c r="Y4" s="3" t="n">
         <v>1.8805</v>
       </c>
-      <c r="Z4" s="4" t="n">
+      <c r="Z4" s="5" t="n">
         <v>1.8805</v>
       </c>
-      <c r="AA4" s="0" t="n">
+      <c r="AA4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AB4" s="0" t="n">
+      <c r="AB4" s="3" t="n">
         <v>1.731</v>
       </c>
-      <c r="AC4" s="4" t="n">
+      <c r="AC4" s="5" t="n">
         <v>1.731</v>
       </c>
-      <c r="AD4" s="4" t="n">
+      <c r="AD4" s="5" t="n">
         <v>1.8657</v>
       </c>
-      <c r="AE4" s="0" t="n">
+      <c r="AE4" s="3" t="n">
         <v>1.8657</v>
       </c>
-      <c r="AF4" s="0" t="n">
+      <c r="AF4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AG4" s="0" t="n">
+      <c r="AG4" s="3" t="n">
         <v>1.7668</v>
       </c>
-      <c r="AH4" s="4" t="n">
+      <c r="AH4" s="5" t="n">
         <v>1.7668</v>
       </c>
-      <c r="AI4" s="4" t="n">
+      <c r="AI4" s="5" t="n">
         <v>1.8451</v>
       </c>
-      <c r="AJ4" s="0" t="n">
+      <c r="AJ4" s="3" t="n">
         <v>1.8451</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="C5" s="0" t="n">
+      <c r="C5" s="3" t="n">
         <v>1.8052</v>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="D5" s="3" t="n">
         <v>1.8293</v>
       </c>
-      <c r="E5" s="0" t="n">
+      <c r="E5" s="3" t="n">
         <v>1.7808</v>
       </c>
-      <c r="F5" s="0" t="n">
+      <c r="F5" s="3" t="n">
         <v>1.817</v>
       </c>
-      <c r="G5" s="0" t="n">
+      <c r="G5" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="H5" s="0" t="n">
+      <c r="H5" s="3" t="n">
         <v>1.8046</v>
       </c>
-      <c r="I5" s="0" t="n">
+      <c r="I5" s="3" t="n">
         <v>1.8282</v>
       </c>
-      <c r="J5" s="0" t="n">
+      <c r="J5" s="3" t="n">
         <v>1.784</v>
       </c>
-      <c r="K5" s="0" t="n">
+      <c r="K5" s="3" t="n">
         <v>1.8162</v>
       </c>
-      <c r="L5" s="0" t="n">
+      <c r="L5" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="M5" s="4" t="n">
+      <c r="M5" s="5" t="n">
         <v>1.5108</v>
       </c>
-      <c r="N5" s="4" t="n">
+      <c r="N5" s="5" t="n">
         <v>1.4011</v>
       </c>
-      <c r="O5" s="4" t="n">
+      <c r="O5" s="5" t="n">
         <v>1.895</v>
       </c>
-      <c r="P5" s="4" t="n">
+      <c r="P5" s="5" t="n">
         <v>1.8875</v>
       </c>
-      <c r="Q5" s="0" t="n">
+      <c r="Q5" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="R5" s="0" t="n">
+      <c r="R5" s="3" t="n">
         <v>1.6346</v>
       </c>
-      <c r="S5" s="0" t="n">
+      <c r="S5" s="3" t="n">
         <v>1.6507</v>
       </c>
-      <c r="T5" s="0" t="n">
+      <c r="T5" s="3" t="n">
         <v>1.8657</v>
       </c>
-      <c r="U5" s="0" t="n">
+      <c r="U5" s="3" t="n">
         <v>1.8859</v>
       </c>
-      <c r="V5" s="4" t="n">
+      <c r="V5" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="W5" s="0" t="n">
+      <c r="W5" s="3" t="n">
         <v>1.7069</v>
       </c>
-      <c r="X5" s="0" t="n">
+      <c r="X5" s="3" t="n">
         <v>1.7077</v>
       </c>
-      <c r="Y5" s="0" t="n">
+      <c r="Y5" s="3" t="n">
         <v>1.8678</v>
       </c>
-      <c r="Z5" s="0" t="n">
+      <c r="Z5" s="3" t="n">
         <v>1.8743</v>
       </c>
-      <c r="AA5" s="0" t="n">
+      <c r="AA5" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="AB5" s="0" t="n">
+      <c r="AB5" s="3" t="n">
         <v>1.738</v>
       </c>
-      <c r="AC5" s="4" t="n">
+      <c r="AC5" s="5" t="n">
         <v>1.7394</v>
       </c>
-      <c r="AD5" s="4" t="n">
+      <c r="AD5" s="5" t="n">
         <v>1.8584</v>
       </c>
-      <c r="AE5" s="0" t="n">
+      <c r="AE5" s="3" t="n">
         <v>1.862</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="C6" s="0" t="n">
+      <c r="C6" s="3" t="n">
         <v>1.8057</v>
       </c>
-      <c r="D6" s="0" t="n">
+      <c r="D6" s="3" t="n">
         <v>1.8234</v>
       </c>
-      <c r="E6" s="0" t="n">
+      <c r="E6" s="3" t="n">
         <v>1.7921</v>
       </c>
-      <c r="F6" s="0" t="n">
+      <c r="F6" s="3" t="n">
         <v>1.8146</v>
       </c>
-      <c r="G6" s="0" t="n">
+      <c r="G6" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="H6" s="0" t="n">
+      <c r="H6" s="3" t="n">
         <v>1.8055</v>
       </c>
-      <c r="I6" s="0" t="n">
+      <c r="I6" s="3" t="n">
         <v>1.8227</v>
       </c>
-      <c r="J6" s="0" t="n">
+      <c r="J6" s="3" t="n">
         <v>1.7932</v>
       </c>
-      <c r="K6" s="0" t="n">
+      <c r="K6" s="3" t="n">
         <v>1.8144</v>
       </c>
-      <c r="L6" s="0" t="n">
+      <c r="L6" s="3" t="n">
         <v>1.75</v>
       </c>
-      <c r="M6" s="0" t="n">
+      <c r="M6" s="3" t="n">
         <v>1.5499</v>
       </c>
-      <c r="N6" s="0" t="n">
+      <c r="N6" s="3" t="n">
         <v>1.5946</v>
       </c>
-      <c r="O6" s="0" t="n">
+      <c r="O6" s="3" t="n">
         <v>1.8408</v>
       </c>
-      <c r="P6" s="0" t="n">
+      <c r="P6" s="3" t="n">
         <v>1.8749</v>
       </c>
-      <c r="Q6" s="0" t="n">
+      <c r="Q6" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="R6" s="0" t="n">
+      <c r="R6" s="3" t="n">
         <v>1.7015</v>
       </c>
-      <c r="S6" s="0" t="n">
+      <c r="S6" s="3" t="n">
         <v>1.7052</v>
       </c>
-      <c r="T6" s="0" t="n">
+      <c r="T6" s="3" t="n">
         <v>1.8351</v>
       </c>
-      <c r="U6" s="0" t="n">
+      <c r="U6" s="3" t="n">
         <v>1.8663</v>
       </c>
-      <c r="V6" s="4" t="n">
+      <c r="V6" s="5" t="n">
         <v>2.5</v>
       </c>
-      <c r="W6" s="0" t="n">
+      <c r="W6" s="3" t="n">
         <v>1.7127</v>
       </c>
-      <c r="X6" s="0" t="n">
+      <c r="X6" s="3" t="n">
         <v>1.7141</v>
       </c>
-      <c r="Y6" s="0" t="n">
+      <c r="Y6" s="3" t="n">
         <v>1.862</v>
       </c>
-      <c r="Z6" s="0" t="n">
+      <c r="Z6" s="3" t="n">
         <v>1.8717</v>
       </c>
-      <c r="AA6" s="0" t="n">
+      <c r="AA6" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="AB6" s="0" t="n">
+      <c r="AB6" s="3" t="n">
         <v>1.7452</v>
       </c>
-      <c r="AC6" s="4" t="n">
+      <c r="AC6" s="5" t="n">
         <v>1.7488</v>
       </c>
-      <c r="AD6" s="4" t="n">
+      <c r="AD6" s="5" t="n">
         <v>1.8504</v>
       </c>
-      <c r="AE6" s="0" t="n">
+      <c r="AE6" s="3" t="n">
         <v>1.8578</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="0" t="n">
+      <c r="B7" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="C7" s="0" t="n">
+      <c r="C7" s="3" t="n">
         <v>1.8063</v>
       </c>
-      <c r="D7" s="0" t="n">
+      <c r="D7" s="3" t="n">
         <v>1.8195</v>
       </c>
-      <c r="E7" s="0" t="n">
+      <c r="E7" s="3" t="n">
         <v>1.7977</v>
       </c>
-      <c r="F7" s="0" t="n">
+      <c r="F7" s="3" t="n">
         <v>1.8133</v>
       </c>
-      <c r="G7" s="0" t="n">
+      <c r="G7" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="H7" s="0" t="n">
+      <c r="H7" s="3" t="n">
         <v>1.8063</v>
       </c>
-      <c r="I7" s="0" t="n">
+      <c r="I7" s="3" t="n">
         <v>1.8191</v>
       </c>
-      <c r="J7" s="0" t="n">
+      <c r="J7" s="3" t="n">
         <v>1.7982</v>
       </c>
-      <c r="K7" s="0" t="n">
+      <c r="K7" s="3" t="n">
         <v>1.8131</v>
       </c>
-      <c r="L7" s="0" t="n">
+      <c r="L7" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="M7" s="0" t="n">
+      <c r="M7" s="3" t="n">
         <v>1.5039</v>
       </c>
-      <c r="N7" s="0" t="n">
+      <c r="N7" s="3" t="n">
         <v>1.6023</v>
       </c>
-      <c r="O7" s="0" t="n">
+      <c r="O7" s="3" t="n">
         <v>1.8226</v>
       </c>
-      <c r="P7" s="0" t="n">
+      <c r="P7" s="3" t="n">
         <v>1.8811</v>
       </c>
-      <c r="Q7" s="0" t="n">
+      <c r="Q7" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="R7" s="0" t="n">
+      <c r="R7" s="3" t="n">
         <v>1.7257</v>
       </c>
-      <c r="S7" s="0" t="n">
+      <c r="S7" s="3" t="n">
         <v>1.7366</v>
       </c>
-      <c r="T7" s="0" t="n">
+      <c r="T7" s="3" t="n">
         <v>1.818</v>
       </c>
-      <c r="U7" s="0" t="n">
+      <c r="U7" s="3" t="n">
         <v>1.8576</v>
       </c>
-      <c r="V7" s="4" t="n">
+      <c r="V7" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="W7" s="0" t="n">
+      <c r="W7" s="3" t="n">
         <v>1.7343</v>
       </c>
-      <c r="X7" s="0" t="n">
+      <c r="X7" s="3" t="n">
         <v>1.74</v>
       </c>
-      <c r="Y7" s="0" t="n">
+      <c r="Y7" s="3" t="n">
         <v>1.8425</v>
       </c>
-      <c r="Z7" s="0" t="n">
+      <c r="Z7" s="3" t="n">
         <v>1.8608</v>
       </c>
-      <c r="AA7" s="0" t="n">
+      <c r="AA7" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="AB7" s="0" t="n">
+      <c r="AB7" s="3" t="n">
         <v>1.7534</v>
       </c>
-      <c r="AC7" s="4" t="n">
+      <c r="AC7" s="5" t="n">
         <v>1.7608</v>
       </c>
-      <c r="AD7" s="4" t="n">
+      <c r="AD7" s="5" t="n">
         <v>1.8408</v>
       </c>
-      <c r="AE7" s="0" t="n">
+      <c r="AE7" s="3" t="n">
         <v>1.8524</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="0" t="n">
+      <c r="B8" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="C8" s="0" t="n">
+      <c r="C8" s="3" t="n">
         <v>1.8069</v>
       </c>
-      <c r="D8" s="0" t="n">
+      <c r="D8" s="3" t="n">
         <v>1.8169</v>
       </c>
-      <c r="E8" s="0" t="n">
+      <c r="E8" s="3" t="n">
         <v>1.801</v>
       </c>
-      <c r="F8" s="0" t="n">
+      <c r="F8" s="3" t="n">
         <v>1.8124</v>
       </c>
-      <c r="L8" s="0" t="n">
+      <c r="L8" s="3" t="n">
         <v>2.25</v>
       </c>
-      <c r="M8" s="0" t="n">
+      <c r="M8" s="3" t="n">
         <v>1.4845</v>
       </c>
-      <c r="N8" s="0" t="n">
+      <c r="N8" s="3" t="n">
         <v>1.5976</v>
       </c>
-      <c r="O8" s="0" t="n">
+      <c r="O8" s="3" t="n">
         <v>1.8087</v>
       </c>
-      <c r="P8" s="0" t="n">
+      <c r="P8" s="3" t="n">
         <v>1.8879</v>
       </c>
-      <c r="Q8" s="0" t="n">
+      <c r="Q8" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="R8" s="0" t="n">
+      <c r="R8" s="3" t="n">
         <v>1.7388</v>
       </c>
-      <c r="S8" s="0" t="n">
+      <c r="S8" s="3" t="n">
         <v>1.7704</v>
       </c>
-      <c r="T8" s="0" t="n">
+      <c r="T8" s="3" t="n">
         <v>1.7998</v>
       </c>
-      <c r="U8" s="0" t="n">
+      <c r="U8" s="3" t="n">
         <v>1.8464</v>
       </c>
-      <c r="V8" s="0" t="n">
+      <c r="V8" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="W8" s="0" t="n">
+      <c r="W8" s="3" t="n">
         <v>1.7471</v>
       </c>
-      <c r="X8" s="0" t="n">
+      <c r="X8" s="3" t="n">
         <v>1.7608</v>
       </c>
-      <c r="Y8" s="0" t="n">
+      <c r="Y8" s="3" t="n">
         <v>1.8286</v>
       </c>
-      <c r="Z8" s="0" t="n">
+      <c r="Z8" s="3" t="n">
         <v>1.8523</v>
       </c>
-      <c r="AA8" s="0" t="n">
+      <c r="AA8" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="AB8" s="0" t="n">
+      <c r="AB8" s="3" t="n">
         <v>1.7685</v>
       </c>
-      <c r="AC8" s="4" t="n">
+      <c r="AC8" s="5" t="n">
         <v>1.7882</v>
       </c>
-      <c r="AD8" s="4" t="n">
+      <c r="AD8" s="5" t="n">
         <v>1.8211</v>
       </c>
-      <c r="AE8" s="0" t="n">
+      <c r="AE8" s="3" t="n">
         <v>1.84</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L9" s="0" t="n">
+      <c r="L9" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="M9" s="0" t="n">
+      <c r="M9" s="3" t="n">
         <v>1.5876</v>
       </c>
-      <c r="N9" s="0" t="n">
+      <c r="N9" s="3" t="n">
         <v>1.6128</v>
       </c>
-      <c r="O9" s="0" t="n">
+      <c r="O9" s="3" t="n">
         <v>1.7999</v>
       </c>
-      <c r="P9" s="0" t="n">
+      <c r="P9" s="3" t="n">
         <v>1.8806</v>
       </c>
-      <c r="Q9" s="0" t="n">
+      <c r="Q9" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="R9" s="0" t="n">
+      <c r="R9" s="3" t="n">
         <v>1.7615</v>
       </c>
-      <c r="S9" s="0" t="n">
+      <c r="S9" s="3" t="n">
         <v>1.8209</v>
       </c>
-      <c r="T9" s="0" t="n">
+      <c r="T9" s="3" t="n">
         <v>1.778</v>
       </c>
-      <c r="U9" s="0" t="n">
+      <c r="U9" s="3" t="n">
         <v>1.8246</v>
       </c>
-      <c r="V9" s="0" t="n">
+      <c r="V9" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="W9" s="0" t="n">
+      <c r="W9" s="3" t="n">
         <v>1.7579</v>
       </c>
-      <c r="X9" s="0" t="n">
+      <c r="X9" s="3" t="n">
         <v>1.7818</v>
       </c>
-      <c r="Y9" s="0" t="n">
+      <c r="Y9" s="3" t="n">
         <v>1.8156</v>
       </c>
-      <c r="Z9" s="0" t="n">
+      <c r="Z9" s="3" t="n">
         <v>1.8438</v>
       </c>
-      <c r="AA9" s="0" t="n">
+      <c r="AA9" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AB9" s="0" t="n">
+      <c r="AB9" s="3" t="n">
         <v>1.7792</v>
       </c>
-      <c r="AC9" s="0" t="n">
+      <c r="AC9" s="3" t="n">
         <v>1.8118</v>
       </c>
-      <c r="AD9" s="0" t="n">
+      <c r="AD9" s="3" t="n">
         <v>1.8049</v>
       </c>
-      <c r="AE9" s="0" t="n">
+      <c r="AE9" s="3" t="n">
         <v>1.8287</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L10" s="0" t="n">
+      <c r="L10" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="M10" s="0" t="n">
+      <c r="M10" s="3" t="n">
         <v>1.6658</v>
       </c>
-      <c r="N10" s="0" t="n">
+      <c r="N10" s="3" t="n">
         <v>1.6465</v>
       </c>
-      <c r="O10" s="0" t="n">
+      <c r="O10" s="3" t="n">
         <v>1.8104</v>
       </c>
-      <c r="P10" s="0" t="n">
+      <c r="P10" s="3" t="n">
         <v>1.8642</v>
       </c>
-      <c r="Q10" s="0" t="n">
+      <c r="Q10" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="R10" s="0" t="n">
+      <c r="R10" s="3" t="n">
         <v>1.7766</v>
       </c>
-      <c r="S10" s="0" t="n">
+      <c r="S10" s="3" t="n">
         <v>1.845</v>
       </c>
-      <c r="T10" s="0" t="n">
+      <c r="T10" s="3" t="n">
         <v>1.7622</v>
       </c>
-      <c r="U10" s="0" t="n">
+      <c r="U10" s="3" t="n">
         <v>1.8164</v>
       </c>
-      <c r="V10" s="0" t="n">
+      <c r="V10" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="W10" s="0" t="n">
+      <c r="W10" s="3" t="n">
         <v>1.7664</v>
       </c>
-      <c r="X10" s="0" t="n">
+      <c r="X10" s="3" t="n">
         <v>1.8006</v>
       </c>
-      <c r="Y10" s="0" t="n">
+      <c r="Y10" s="3" t="n">
         <v>1.8046</v>
       </c>
-      <c r="Z10" s="0" t="n">
+      <c r="Z10" s="3" t="n">
         <v>1.8358</v>
       </c>
-      <c r="AA10" s="0" t="n">
+      <c r="AA10" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="AB10" s="0" t="n">
+      <c r="AB10" s="3" t="n">
         <v>1.7832</v>
       </c>
-      <c r="AC10" s="0" t="n">
+      <c r="AC10" s="3" t="n">
         <v>1.82</v>
       </c>
-      <c r="AD10" s="0" t="n">
+      <c r="AD10" s="3" t="n">
         <v>1.7989</v>
       </c>
-      <c r="AE10" s="0" t="n">
+      <c r="AE10" s="3" t="n">
         <v>1.8244</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L11" s="0" t="n">
+      <c r="L11" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="M11" s="0" t="n">
+      <c r="M11" s="3" t="n">
         <v>1.6879</v>
       </c>
-      <c r="N11" s="0" t="n">
+      <c r="N11" s="3" t="n">
         <v>1.6719</v>
       </c>
-      <c r="O11" s="0" t="n">
+      <c r="O11" s="3" t="n">
         <v>1.8167</v>
       </c>
-      <c r="P11" s="0" t="n">
+      <c r="P11" s="3" t="n">
         <v>1.8567</v>
       </c>
-      <c r="Q11" s="0" t="n">
+      <c r="Q11" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="R11" s="0" t="n">
+      <c r="R11" s="3" t="n">
         <v>1.7881</v>
       </c>
-      <c r="S11" s="0" t="n">
+      <c r="S11" s="3" t="n">
         <v>1.8454</v>
       </c>
-      <c r="T11" s="0" t="n">
+      <c r="T11" s="3" t="n">
         <v>1.7641</v>
       </c>
-      <c r="U11" s="0" t="n">
+      <c r="U11" s="3" t="n">
         <v>1.8157</v>
       </c>
-      <c r="V11" s="0" t="n">
+      <c r="V11" s="3" t="n">
         <v>7.5</v>
       </c>
-      <c r="W11" s="0" t="n">
+      <c r="W11" s="3" t="n">
         <v>1.7698</v>
       </c>
-      <c r="X11" s="0" t="n">
+      <c r="X11" s="3" t="n">
         <v>1.8087</v>
       </c>
-      <c r="Y11" s="0" t="n">
+      <c r="Y11" s="3" t="n">
         <v>1.7999</v>
       </c>
-      <c r="Z11" s="0" t="n">
+      <c r="Z11" s="3" t="n">
         <v>1.8321</v>
       </c>
-      <c r="AA11" s="0" t="n">
+      <c r="AA11" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="AB11" s="0" t="n">
+      <c r="AB11" s="3" t="n">
         <v>1.7868</v>
       </c>
-      <c r="AC11" s="0" t="n">
+      <c r="AC11" s="3" t="n">
         <v>1.8255</v>
       </c>
-      <c r="AD11" s="0" t="n">
+      <c r="AD11" s="3" t="n">
         <v>1.7944</v>
       </c>
-      <c r="AE11" s="0" t="n">
+      <c r="AE11" s="3" t="n">
         <v>1.8212</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L12" s="0" t="n">
+      <c r="L12" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="M12" s="0" t="n">
+      <c r="M12" s="3" t="n">
         <v>1.711</v>
       </c>
-      <c r="N12" s="0" t="n">
+      <c r="N12" s="3" t="n">
         <v>1.7192</v>
       </c>
-      <c r="O12" s="0" t="n">
+      <c r="O12" s="3" t="n">
         <v>1.8028</v>
       </c>
-      <c r="P12" s="0" t="n">
+      <c r="P12" s="3" t="n">
         <v>1.8603</v>
       </c>
-      <c r="Q12" s="0" t="n">
+      <c r="Q12" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="R12" s="0" t="n">
+      <c r="R12" s="3" t="n">
         <v>1.7968</v>
       </c>
-      <c r="S12" s="0" t="n">
+      <c r="S12" s="3" t="n">
         <v>1.8391</v>
       </c>
-      <c r="T12" s="0" t="n">
+      <c r="T12" s="3" t="n">
         <v>1.7712</v>
       </c>
-      <c r="U12" s="0" t="n">
+      <c r="U12" s="3" t="n">
         <v>1.8169</v>
       </c>
-      <c r="V12" s="0" t="n">
+      <c r="V12" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="W12" s="0" t="n">
+      <c r="W12" s="3" t="n">
         <v>1.7727</v>
       </c>
-      <c r="X12" s="0" t="n">
+      <c r="X12" s="3" t="n">
         <v>1.8159</v>
       </c>
-      <c r="Y12" s="0" t="n">
+      <c r="Y12" s="3" t="n">
         <v>1.7956</v>
       </c>
-      <c r="Z12" s="0" t="n">
+      <c r="Z12" s="3" t="n">
         <v>1.8286</v>
       </c>
-      <c r="AA12" s="0" t="n">
+      <c r="AA12" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="AB12" s="0" t="n">
+      <c r="AB12" s="3" t="n">
         <v>1.7932</v>
       </c>
-      <c r="AC12" s="0" t="n">
+      <c r="AC12" s="3" t="n">
         <v>1.8296</v>
       </c>
-      <c r="AD12" s="0" t="n">
+      <c r="AD12" s="3" t="n">
         <v>1.7897</v>
       </c>
-      <c r="AE12" s="0" t="n">
+      <c r="AE12" s="3" t="n">
         <v>1.8177</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L13" s="0" t="n">
+      <c r="L13" s="3" t="n">
         <v>5.25</v>
       </c>
-      <c r="M13" s="0" t="n">
+      <c r="M13" s="3" t="n">
         <v>1.7141</v>
       </c>
-      <c r="N13" s="0" t="n">
+      <c r="N13" s="3" t="n">
         <v>1.7316</v>
       </c>
-      <c r="O13" s="0" t="n">
+      <c r="O13" s="3" t="n">
         <v>1.7965</v>
       </c>
-      <c r="P13" s="0" t="n">
+      <c r="P13" s="3" t="n">
         <v>1.8591</v>
       </c>
-      <c r="Q13" s="0" t="n">
+      <c r="Q13" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="R13" s="0" t="n">
+      <c r="R13" s="3" t="n">
         <v>1.8016</v>
       </c>
-      <c r="S13" s="0" t="n">
+      <c r="S13" s="3" t="n">
         <v>1.8314</v>
       </c>
-      <c r="T13" s="0" t="n">
+      <c r="T13" s="3" t="n">
         <v>1.7818</v>
       </c>
-      <c r="U13" s="0" t="n">
+      <c r="U13" s="3" t="n">
         <v>1.8164</v>
       </c>
-      <c r="V13" s="0" t="n">
+      <c r="V13" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="W13" s="0" t="n">
+      <c r="W13" s="3" t="n">
         <v>1.7825</v>
       </c>
-      <c r="X13" s="0" t="n">
+      <c r="X13" s="3" t="n">
         <v>1.8337</v>
       </c>
-      <c r="Y13" s="0" t="n">
+      <c r="Y13" s="3" t="n">
         <v>1.7836</v>
       </c>
-      <c r="Z13" s="0" t="n">
+      <c r="Z13" s="3" t="n">
         <v>1.8199</v>
       </c>
-      <c r="AA13" s="0" t="n">
+      <c r="AA13" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="AB13" s="0" t="n">
+      <c r="AB13" s="3" t="n">
         <v>1.7982</v>
       </c>
-      <c r="AC13" s="0" t="n">
+      <c r="AC13" s="3" t="n">
         <v>1.8284</v>
       </c>
-      <c r="AD13" s="0" t="n">
+      <c r="AD13" s="3" t="n">
         <v>1.7898</v>
       </c>
-      <c r="AE13" s="0" t="n">
+      <c r="AE13" s="3" t="n">
         <v>1.8162</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L14" s="0" t="n">
+      <c r="L14" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="M14" s="0" t="n">
+      <c r="M14" s="3" t="n">
         <v>1.7112</v>
       </c>
-      <c r="N14" s="0" t="n">
+      <c r="N14" s="3" t="n">
         <v>1.7633</v>
       </c>
-      <c r="O14" s="0" t="n">
+      <c r="O14" s="3" t="n">
         <v>1.7774</v>
       </c>
-      <c r="P14" s="0" t="n">
+      <c r="P14" s="3" t="n">
         <v>1.8475</v>
       </c>
-      <c r="Q14" s="0" t="n">
+      <c r="Q14" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="R14" s="0" t="n">
+      <c r="R14" s="3" t="n">
         <v>1.804</v>
       </c>
-      <c r="S14" s="0" t="n">
+      <c r="S14" s="3" t="n">
         <v>1.8254</v>
       </c>
-      <c r="T14" s="0" t="n">
+      <c r="T14" s="3" t="n">
         <v>1.7903</v>
       </c>
-      <c r="U14" s="0" t="n">
+      <c r="U14" s="3" t="n">
         <v>1.8151</v>
       </c>
-      <c r="V14" s="0" t="n">
+      <c r="V14" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="W14" s="0" t="n">
+      <c r="W14" s="3" t="n">
         <v>1.7909</v>
       </c>
-      <c r="X14" s="0" t="n">
+      <c r="X14" s="3" t="n">
         <v>1.8368</v>
       </c>
-      <c r="Y14" s="0" t="n">
+      <c r="Y14" s="3" t="n">
         <v>1.7799</v>
       </c>
-      <c r="Z14" s="0" t="n">
+      <c r="Z14" s="3" t="n">
         <v>1.8171</v>
       </c>
-      <c r="AA14" s="0" t="n">
+      <c r="AA14" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="AB14" s="0" t="n">
+      <c r="AB14" s="3" t="n">
         <v>1.8017</v>
       </c>
-      <c r="AC14" s="0" t="n">
+      <c r="AC14" s="3" t="n">
         <v>1.8252</v>
       </c>
-      <c r="AD14" s="0" t="n">
+      <c r="AD14" s="3" t="n">
         <v>1.7925</v>
       </c>
-      <c r="AE14" s="0" t="n">
+      <c r="AE14" s="3" t="n">
         <v>1.8152</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L15" s="0" t="n">
+      <c r="L15" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="M15" s="0" t="n">
+      <c r="M15" s="3" t="n">
         <v>1.7421</v>
       </c>
-      <c r="N15" s="0" t="n">
+      <c r="N15" s="3" t="n">
         <v>1.7997</v>
       </c>
-      <c r="O15" s="0" t="n">
+      <c r="O15" s="3" t="n">
         <v>1.7679</v>
       </c>
-      <c r="P15" s="0" t="n">
+      <c r="P15" s="3" t="n">
         <v>1.8344</v>
       </c>
-      <c r="Q15" s="0" t="n">
+      <c r="Q15" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="R15" s="0" t="n">
+      <c r="R15" s="3" t="n">
         <v>1.8054</v>
       </c>
-      <c r="S15" s="0" t="n">
+      <c r="S15" s="3" t="n">
         <v>1.8212</v>
       </c>
-      <c r="T15" s="0" t="n">
+      <c r="T15" s="3" t="n">
         <v>1.7959</v>
       </c>
-      <c r="U15" s="0" t="n">
+      <c r="U15" s="3" t="n">
         <v>1.8139</v>
       </c>
-      <c r="V15" s="0" t="n">
+      <c r="V15" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="W15" s="0" t="n">
+      <c r="W15" s="3" t="n">
         <v>1.7973</v>
       </c>
-      <c r="X15" s="0" t="n">
+      <c r="X15" s="3" t="n">
         <v>1.8334</v>
       </c>
-      <c r="Y15" s="0" t="n">
+      <c r="Y15" s="3" t="n">
         <v>1.7824</v>
       </c>
-      <c r="Z15" s="0" t="n">
+      <c r="Z15" s="3" t="n">
         <v>1.8164</v>
       </c>
-      <c r="AA15" s="0" t="n">
+      <c r="AA15" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="AB15" s="0" t="n">
+      <c r="AB15" s="3" t="n">
         <v>1.804</v>
       </c>
-      <c r="AC15" s="0" t="n">
+      <c r="AC15" s="3" t="n">
         <v>1.8218</v>
       </c>
-      <c r="AD15" s="0" t="n">
+      <c r="AD15" s="3" t="n">
         <v>1.7959</v>
       </c>
-      <c r="AE15" s="0" t="n">
+      <c r="AE15" s="3" t="n">
         <v>1.8143</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L16" s="0" t="n">
+      <c r="L16" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="M16" s="0" t="n">
+      <c r="M16" s="3" t="n">
         <v>1.7476</v>
       </c>
-      <c r="N16" s="0" t="n">
+      <c r="N16" s="3" t="n">
         <v>1.8237</v>
       </c>
-      <c r="O16" s="0" t="n">
+      <c r="O16" s="3" t="n">
         <v>1.7648</v>
       </c>
-      <c r="P16" s="0" t="n">
+      <c r="P16" s="3" t="n">
         <v>1.8165</v>
       </c>
-      <c r="V16" s="0" t="n">
+      <c r="V16" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="W16" s="0" t="n">
+      <c r="W16" s="3" t="n">
         <v>1.7997</v>
       </c>
-      <c r="X16" s="0" t="n">
+      <c r="X16" s="3" t="n">
         <v>1.8309</v>
       </c>
-      <c r="Y16" s="0" t="n">
+      <c r="Y16" s="3" t="n">
         <v>1.785</v>
       </c>
-      <c r="Z16" s="0" t="n">
+      <c r="Z16" s="3" t="n">
         <v>1.8161</v>
       </c>
-      <c r="AA16" s="0" t="n">
+      <c r="AA16" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="AB16" s="0" t="n">
+      <c r="AB16" s="3" t="n">
         <v>1.8054</v>
       </c>
-      <c r="AC16" s="0" t="n">
+      <c r="AC16" s="3" t="n">
         <v>1.8191</v>
       </c>
-      <c r="AD16" s="0" t="n">
+      <c r="AD16" s="3" t="n">
         <v>1.7989</v>
       </c>
-      <c r="AE16" s="0" t="n">
+      <c r="AE16" s="3" t="n">
         <v>1.8134</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L17" s="0" t="n">
+      <c r="L17" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="M17" s="0" t="n">
+      <c r="M17" s="3" t="n">
         <v>1.7737</v>
       </c>
-      <c r="N17" s="0" t="n">
+      <c r="N17" s="3" t="n">
         <v>1.8533</v>
       </c>
-      <c r="O17" s="0" t="n">
+      <c r="O17" s="3" t="n">
         <v>1.7375</v>
       </c>
-      <c r="P17" s="0" t="n">
+      <c r="P17" s="3" t="n">
         <v>1.8133</v>
       </c>
-      <c r="V17" s="0" t="n">
+      <c r="V17" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="W17" s="4" t="n">
+      <c r="W17" s="5" t="n">
         <v>1.8015</v>
       </c>
-      <c r="X17" s="4" t="n">
+      <c r="X17" s="5" t="n">
         <v>1.8283</v>
       </c>
-      <c r="Y17" s="4" t="n">
+      <c r="Y17" s="5" t="n">
         <v>1.7879</v>
       </c>
-      <c r="Z17" s="4" t="n">
+      <c r="Z17" s="5" t="n">
         <v>1.8157</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L18" s="0" t="n">
+      <c r="L18" s="3" t="n">
         <v>10.5</v>
       </c>
-      <c r="M18" s="0" t="n">
+      <c r="M18" s="3" t="n">
         <v>1.7778</v>
       </c>
-      <c r="N18" s="0" t="n">
+      <c r="N18" s="3" t="n">
         <v>1.8505</v>
       </c>
-      <c r="O18" s="0" t="n">
+      <c r="O18" s="3" t="n">
         <v>1.7428</v>
       </c>
-      <c r="P18" s="0" t="n">
+      <c r="P18" s="3" t="n">
         <v>1.8142</v>
       </c>
-      <c r="V18" s="0" t="n">
+      <c r="V18" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="W18" s="0" t="n">
+      <c r="W18" s="3" t="n">
         <v>1.8039</v>
       </c>
-      <c r="X18" s="0" t="n">
+      <c r="X18" s="3" t="n">
         <v>1.8236</v>
       </c>
-      <c r="Y18" s="0" t="n">
+      <c r="Y18" s="3" t="n">
         <v>1.7932</v>
       </c>
-      <c r="Z18" s="0" t="n">
+      <c r="Z18" s="3" t="n">
         <v>1.8146</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L19" s="0" t="n">
+      <c r="L19" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="M19" s="0" t="n">
+      <c r="M19" s="3" t="n">
         <v>1.7856</v>
       </c>
-      <c r="N19" s="0" t="n">
+      <c r="N19" s="3" t="n">
         <v>1.8499</v>
       </c>
-      <c r="O19" s="0" t="n">
+      <c r="O19" s="3" t="n">
         <v>1.7519</v>
       </c>
-      <c r="P19" s="0" t="n">
+      <c r="P19" s="3" t="n">
         <v>1.8135</v>
       </c>
-      <c r="V19" s="0" t="n">
+      <c r="V19" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="W19" s="0" t="n">
+      <c r="W19" s="3" t="n">
         <v>1.8053</v>
       </c>
-      <c r="X19" s="0" t="n">
+      <c r="X19" s="3" t="n">
         <v>1.8201</v>
       </c>
-      <c r="Y19" s="0" t="n">
+      <c r="Y19" s="3" t="n">
         <v>1.7974</v>
       </c>
-      <c r="Z19" s="0" t="n">
+      <c r="Z19" s="3" t="n">
         <v>1.8136</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L20" s="0" t="n">
+      <c r="L20" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="M20" s="0" t="n">
+      <c r="M20" s="3" t="n">
         <v>1.7969</v>
       </c>
-      <c r="N20" s="0" t="n">
+      <c r="N20" s="3" t="n">
         <v>1.8422</v>
       </c>
-      <c r="O20" s="0" t="n">
+      <c r="O20" s="3" t="n">
         <v>1.7632</v>
       </c>
-      <c r="P20" s="0" t="n">
+      <c r="P20" s="3" t="n">
         <v>1.8175</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L21" s="0" t="n">
+      <c r="L21" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="M21" s="0" t="n">
+      <c r="M21" s="3" t="n">
         <v>1.8019</v>
       </c>
-      <c r="N21" s="0" t="n">
+      <c r="N21" s="3" t="n">
         <v>1.833</v>
       </c>
-      <c r="O21" s="0" t="n">
+      <c r="O21" s="3" t="n">
         <v>1.7781</v>
       </c>
-      <c r="P21" s="0" t="n">
+      <c r="P21" s="3" t="n">
         <v>1.8169</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L22" s="0" t="n">
+      <c r="L22" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="M22" s="0" t="n">
+      <c r="M22" s="3" t="n">
         <v>1.8041</v>
       </c>
-      <c r="N22" s="0" t="n">
+      <c r="N22" s="3" t="n">
         <v>1.8263</v>
       </c>
-      <c r="O22" s="0" t="n">
+      <c r="O22" s="3" t="n">
         <v>1.7887</v>
       </c>
-      <c r="P22" s="0" t="n">
+      <c r="P22" s="3" t="n">
         <v>1.8154</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L23" s="0" t="n">
+      <c r="L23" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="M23" s="0" t="n">
+      <c r="M23" s="3" t="n">
         <v>1.8054</v>
       </c>
-      <c r="N23" s="0" t="n">
+      <c r="N23" s="3" t="n">
         <v>1.8216</v>
       </c>
-      <c r="O23" s="0" t="n">
+      <c r="O23" s="3" t="n">
         <v>1.7951</v>
       </c>
-      <c r="P23" s="0" t="n">
+      <c r="P23" s="3" t="n">
         <v>1.814</v>
       </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Обычный"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Обычный"&amp;12Страница &amp;P</oddFooter>
@@ -1638,7 +1763,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -1646,7 +1771,7 @@
   <sheetFormatPr defaultColWidth="11.77734375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="3" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1660,13 +1785,13 @@
       <c r="C2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G2" s="2" t="n">
@@ -1690,1022 +1815,1022 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="F3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="0" t="s">
+      <c r="G3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="0" t="s">
+      <c r="H3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="K3" s="0" t="s">
+      <c r="K3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L3" s="0" t="s">
+      <c r="L3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="0" t="s">
+      <c r="M3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="N3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="O3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="P3" s="0" t="s">
+      <c r="P3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="Q3" s="0" t="s">
+      <c r="Q3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="R3" s="0" t="s">
+      <c r="R3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S3" s="3" t="s">
+      <c r="S3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="T3" s="3" t="s">
+      <c r="T3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="U3" s="0" t="s">
+      <c r="U3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="V3" s="0" t="s">
+      <c r="V3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="W3" s="0" t="s">
+      <c r="W3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X3" s="3" t="s">
+      <c r="X3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="Y3" s="3" t="s">
+      <c r="Y3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="Z3" s="0" t="s">
+      <c r="Z3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="AA3" s="0" t="s">
+      <c r="AA3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="AB3" s="0" t="s">
+      <c r="AB3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC3" s="3" t="s">
+      <c r="AC3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="AD3" s="3" t="s">
+      <c r="AD3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="AE3" s="0" t="s">
+      <c r="AE3" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="6" t="n">
         <v>1.8094</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="C4" s="0" t="n">
+      <c r="C4" s="3" t="n">
         <v>1.7817</v>
       </c>
-      <c r="D4" s="0" t="n">
+      <c r="D4" s="3" t="n">
         <v>1.832</v>
       </c>
-      <c r="E4" s="0" t="n">
+      <c r="E4" s="3" t="n">
         <v>1.7827</v>
       </c>
-      <c r="F4" s="0" t="n">
+      <c r="F4" s="3" t="n">
         <v>1.8307</v>
       </c>
-      <c r="G4" s="0" t="n">
+      <c r="G4" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="H4" s="0" t="n">
+      <c r="H4" s="3" t="n">
         <v>1.7843</v>
       </c>
-      <c r="I4" s="0" t="n">
+      <c r="I4" s="3" t="n">
         <v>1.8302</v>
       </c>
-      <c r="J4" s="0" t="n">
+      <c r="J4" s="3" t="n">
         <v>1.7849</v>
       </c>
-      <c r="K4" s="0" t="n">
+      <c r="K4" s="3" t="n">
         <v>1.8292</v>
       </c>
-      <c r="L4" s="0" t="n">
+      <c r="L4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M4" s="0" t="n">
+      <c r="M4" s="3" t="n">
         <v>1.1471</v>
       </c>
-      <c r="N4" s="0" t="n">
+      <c r="N4" s="3" t="n">
         <v>1.1471</v>
       </c>
-      <c r="O4" s="0" t="n">
+      <c r="O4" s="3" t="n">
         <v>1.9135</v>
       </c>
-      <c r="P4" s="0" t="n">
+      <c r="P4" s="3" t="n">
         <v>1.9135</v>
       </c>
-      <c r="Q4" s="0" t="n">
+      <c r="Q4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="R4" s="0" t="n">
+      <c r="R4" s="3" t="n">
         <v>1.5195</v>
       </c>
-      <c r="S4" s="0" t="n">
+      <c r="S4" s="3" t="n">
         <v>1.5195</v>
       </c>
-      <c r="T4" s="0" t="n">
+      <c r="T4" s="3" t="n">
         <v>1.8998</v>
       </c>
-      <c r="U4" s="0" t="n">
+      <c r="U4" s="3" t="n">
         <v>1.8998</v>
       </c>
-      <c r="V4" s="4" t="n">
+      <c r="V4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="W4" s="0" t="n">
+      <c r="W4" s="3" t="n">
         <v>1.6913</v>
       </c>
-      <c r="X4" s="4" t="n">
+      <c r="X4" s="5" t="n">
         <v>1.6913</v>
       </c>
-      <c r="Y4" s="0" t="n">
+      <c r="Y4" s="3" t="n">
         <v>1.8805</v>
       </c>
-      <c r="Z4" s="4" t="n">
+      <c r="Z4" s="5" t="n">
         <v>1.8805</v>
       </c>
-      <c r="AA4" s="0" t="n">
+      <c r="AA4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AB4" s="0" t="n">
+      <c r="AB4" s="3" t="n">
         <v>1.731</v>
       </c>
-      <c r="AC4" s="4" t="n">
+      <c r="AC4" s="5" t="n">
         <v>1.731</v>
       </c>
-      <c r="AD4" s="4" t="n">
+      <c r="AD4" s="5" t="n">
         <v>1.8657</v>
       </c>
-      <c r="AE4" s="0" t="n">
+      <c r="AE4" s="3" t="n">
         <v>1.8657</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="C5" s="0" t="n">
+      <c r="C5" s="3" t="n">
         <v>1.7893</v>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="D5" s="3" t="n">
         <v>1.8282</v>
       </c>
-      <c r="E5" s="0" t="n">
+      <c r="E5" s="3" t="n">
         <v>1.788</v>
       </c>
-      <c r="F5" s="0" t="n">
+      <c r="F5" s="3" t="n">
         <v>1.8263</v>
       </c>
-      <c r="G5" s="0" t="n">
+      <c r="G5" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="H5" s="0" t="n">
+      <c r="H5" s="3" t="n">
         <v>1.7907</v>
       </c>
-      <c r="I5" s="0" t="n">
+      <c r="I5" s="3" t="n">
         <v>1.827</v>
       </c>
-      <c r="J5" s="0" t="n">
+      <c r="J5" s="3" t="n">
         <v>1.7894</v>
       </c>
-      <c r="K5" s="0" t="n">
+      <c r="K5" s="3" t="n">
         <v>1.8253</v>
       </c>
-      <c r="L5" s="0" t="n">
+      <c r="L5" s="3" t="n">
         <v>1.75</v>
       </c>
-      <c r="M5" s="0" t="n">
+      <c r="M5" s="3" t="n">
         <v>1.5859</v>
       </c>
-      <c r="N5" s="0" t="n">
+      <c r="N5" s="3" t="n">
         <v>1.6135</v>
       </c>
-      <c r="O5" s="0" t="n">
+      <c r="O5" s="3" t="n">
         <v>1.8748</v>
       </c>
-      <c r="P5" s="0" t="n">
+      <c r="P5" s="3" t="n">
         <v>1.8864</v>
       </c>
-      <c r="Q5" s="0" t="n">
+      <c r="Q5" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="R5" s="0" t="n">
+      <c r="R5" s="3" t="n">
         <v>1.636</v>
       </c>
-      <c r="S5" s="0" t="n">
+      <c r="S5" s="3" t="n">
         <v>1.6625</v>
       </c>
-      <c r="T5" s="0" t="n">
+      <c r="T5" s="3" t="n">
         <v>1.8707</v>
       </c>
-      <c r="U5" s="0" t="n">
+      <c r="U5" s="3" t="n">
         <v>1.8911</v>
       </c>
-      <c r="V5" s="0" t="n">
+      <c r="V5" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="W5" s="0" t="n">
+      <c r="W5" s="3" t="n">
         <v>1.7012</v>
       </c>
-      <c r="X5" s="0" t="n">
+      <c r="X5" s="3" t="n">
         <v>1.714</v>
       </c>
-      <c r="Y5" s="0" t="n">
+      <c r="Y5" s="3" t="n">
         <v>1.8646</v>
       </c>
-      <c r="Z5" s="0" t="n">
+      <c r="Z5" s="3" t="n">
         <v>1.8784</v>
       </c>
-      <c r="AA5" s="0" t="n">
+      <c r="AA5" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="AB5" s="0" t="n">
+      <c r="AB5" s="3" t="n">
         <v>1.7345</v>
       </c>
-      <c r="AC5" s="0" t="n">
+      <c r="AC5" s="3" t="n">
         <v>1.7427</v>
       </c>
-      <c r="AD5" s="0" t="n">
+      <c r="AD5" s="3" t="n">
         <v>1.856</v>
       </c>
-      <c r="AE5" s="0" t="n">
+      <c r="AE5" s="3" t="n">
         <v>1.8645</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="C6" s="0" t="n">
+      <c r="C6" s="3" t="n">
         <v>1.7974</v>
       </c>
-      <c r="D6" s="0" t="n">
+      <c r="D6" s="3" t="n">
         <v>1.8229</v>
       </c>
-      <c r="E6" s="0" t="n">
+      <c r="E6" s="3" t="n">
         <v>1.7947</v>
       </c>
-      <c r="F6" s="0" t="n">
+      <c r="F6" s="3" t="n">
         <v>1.8204</v>
       </c>
-      <c r="G6" s="0" t="n">
+      <c r="G6" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="H6" s="0" t="n">
+      <c r="H6" s="3" t="n">
         <v>1.7979</v>
       </c>
-      <c r="I6" s="0" t="n">
+      <c r="I6" s="3" t="n">
         <v>1.8223</v>
       </c>
-      <c r="J6" s="0" t="n">
+      <c r="J6" s="3" t="n">
         <v>1.7954</v>
       </c>
-      <c r="K6" s="0" t="n">
+      <c r="K6" s="3" t="n">
         <v>1.82</v>
       </c>
-      <c r="L6" s="0" t="n">
+      <c r="L6" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="M6" s="0" t="n">
+      <c r="M6" s="3" t="n">
         <v>1.5546</v>
       </c>
-      <c r="N6" s="0" t="n">
+      <c r="N6" s="3" t="n">
         <v>1.6113</v>
       </c>
-      <c r="O6" s="0" t="n">
+      <c r="O6" s="3" t="n">
         <v>1.8692</v>
       </c>
-      <c r="P6" s="0" t="n">
+      <c r="P6" s="3" t="n">
         <v>1.8831</v>
       </c>
-      <c r="Q6" s="0" t="n">
+      <c r="Q6" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="R6" s="0" t="n">
+      <c r="R6" s="3" t="n">
         <v>1.6627</v>
       </c>
-      <c r="S6" s="0" t="n">
+      <c r="S6" s="3" t="n">
         <v>1.7344</v>
       </c>
-      <c r="T6" s="0" t="n">
+      <c r="T6" s="3" t="n">
         <v>1.8194</v>
       </c>
-      <c r="U6" s="0" t="n">
+      <c r="U6" s="3" t="n">
         <v>1.8883</v>
       </c>
-      <c r="V6" s="0" t="n">
+      <c r="V6" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="W6" s="0" t="n">
+      <c r="W6" s="3" t="n">
         <v>1.704</v>
       </c>
-      <c r="X6" s="0" t="n">
+      <c r="X6" s="3" t="n">
         <v>1.7233</v>
       </c>
-      <c r="Y6" s="0" t="n">
+      <c r="Y6" s="3" t="n">
         <v>1.8573</v>
       </c>
-      <c r="Z6" s="0" t="n">
+      <c r="Z6" s="3" t="n">
         <v>1.8778</v>
       </c>
-      <c r="AA6" s="0" t="n">
+      <c r="AA6" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="AB6" s="0" t="n">
+      <c r="AB6" s="3" t="n">
         <v>1.7382</v>
       </c>
-      <c r="AC6" s="0" t="n">
+      <c r="AC6" s="3" t="n">
         <v>1.7553</v>
       </c>
-      <c r="AD6" s="0" t="n">
+      <c r="AD6" s="3" t="n">
         <v>1.8458</v>
       </c>
-      <c r="AE6" s="0" t="n">
+      <c r="AE6" s="3" t="n">
         <v>1.8629</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="0" t="n">
+      <c r="B7" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="C7" s="0" t="n">
+      <c r="C7" s="3" t="n">
         <v>1.8015</v>
       </c>
-      <c r="D7" s="0" t="n">
+      <c r="D7" s="3" t="n">
         <v>1.8194</v>
       </c>
-      <c r="E7" s="0" t="n">
+      <c r="E7" s="3" t="n">
         <v>1.7987</v>
       </c>
-      <c r="F7" s="0" t="n">
+      <c r="F7" s="3" t="n">
         <v>1.8169</v>
       </c>
-      <c r="G7" s="0" t="n">
+      <c r="G7" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="H7" s="0" t="n">
+      <c r="H7" s="3" t="n">
         <v>1.8017</v>
       </c>
-      <c r="I7" s="0" t="n">
+      <c r="I7" s="3" t="n">
         <v>1.8191</v>
       </c>
-      <c r="J7" s="0" t="n">
+      <c r="J7" s="3" t="n">
         <v>1.7991</v>
       </c>
-      <c r="K7" s="0" t="n">
+      <c r="K7" s="3" t="n">
         <v>1.8167</v>
       </c>
-      <c r="L7" s="0" t="n">
+      <c r="L7" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="M7" s="0" t="n">
+      <c r="M7" s="3" t="n">
         <v>1.6169</v>
       </c>
-      <c r="N7" s="0" t="n">
+      <c r="N7" s="3" t="n">
         <v>1.6894</v>
       </c>
-      <c r="O7" s="0" t="n">
+      <c r="O7" s="3" t="n">
         <v>1.8123</v>
       </c>
-      <c r="P7" s="0" t="n">
+      <c r="P7" s="3" t="n">
         <v>1.8931</v>
       </c>
-      <c r="Q7" s="0" t="n">
+      <c r="Q7" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="R7" s="0" t="n">
+      <c r="R7" s="3" t="n">
         <v>1.6883</v>
       </c>
-      <c r="S7" s="0" t="n">
+      <c r="S7" s="3" t="n">
         <v>1.7988</v>
       </c>
-      <c r="T7" s="0" t="n">
+      <c r="T7" s="3" t="n">
         <v>1.7756</v>
       </c>
-      <c r="U7" s="0" t="n">
+      <c r="U7" s="3" t="n">
         <v>1.8721</v>
       </c>
-      <c r="V7" s="0" t="n">
+      <c r="V7" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="W7" s="0" t="n">
+      <c r="W7" s="3" t="n">
         <v>1.7143</v>
       </c>
-      <c r="X7" s="0" t="n">
+      <c r="X7" s="3" t="n">
         <v>1.757</v>
       </c>
-      <c r="Y7" s="0" t="n">
+      <c r="Y7" s="3" t="n">
         <v>1.8325</v>
       </c>
-      <c r="Z7" s="0" t="n">
+      <c r="Z7" s="3" t="n">
         <v>1.8732</v>
       </c>
-      <c r="AA7" s="0" t="n">
+      <c r="AA7" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="AB7" s="0" t="n">
+      <c r="AB7" s="3" t="n">
         <v>1.7425</v>
       </c>
-      <c r="AC7" s="0" t="n">
+      <c r="AC7" s="3" t="n">
         <v>1.7701</v>
       </c>
-      <c r="AD7" s="0" t="n">
+      <c r="AD7" s="3" t="n">
         <v>1.8342</v>
       </c>
-      <c r="AE7" s="0" t="n">
+      <c r="AE7" s="3" t="n">
         <v>1.8604</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L8" s="0" t="n">
+      <c r="L8" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="M8" s="0" t="n">
+      <c r="M8" s="3" t="n">
         <v>1.609</v>
       </c>
-      <c r="N8" s="0" t="n">
+      <c r="N8" s="3" t="n">
         <v>1.7152</v>
       </c>
-      <c r="O8" s="0" t="n">
+      <c r="O8" s="3" t="n">
         <v>1.7909</v>
       </c>
-      <c r="P8" s="0" t="n">
+      <c r="P8" s="3" t="n">
         <v>1.8945</v>
       </c>
-      <c r="Q8" s="0" t="n">
+      <c r="Q8" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="R8" s="0" t="n">
+      <c r="R8" s="3" t="n">
         <v>1.7186</v>
       </c>
-      <c r="S8" s="0" t="n">
+      <c r="S8" s="3" t="n">
         <v>1.83</v>
       </c>
-      <c r="T8" s="0" t="n">
+      <c r="T8" s="3" t="n">
         <v>1.7686</v>
       </c>
-      <c r="U8" s="0" t="n">
+      <c r="U8" s="3" t="n">
         <v>1.8593</v>
       </c>
-      <c r="V8" s="0" t="n">
+      <c r="V8" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="W8" s="0" t="n">
+      <c r="W8" s="3" t="n">
         <v>1.722</v>
       </c>
-      <c r="X8" s="0" t="n">
+      <c r="X8" s="3" t="n">
         <v>1.7795</v>
       </c>
-      <c r="Y8" s="0" t="n">
+      <c r="Y8" s="3" t="n">
         <v>1.8171</v>
       </c>
-      <c r="Z8" s="0" t="n">
+      <c r="Z8" s="3" t="n">
         <v>1.8683</v>
       </c>
-      <c r="AA8" s="0" t="n">
+      <c r="AA8" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="AB8" s="0" t="n">
+      <c r="AB8" s="3" t="n">
         <v>1.7522</v>
       </c>
-      <c r="AC8" s="0" t="n">
+      <c r="AC8" s="3" t="n">
         <v>1.7982</v>
       </c>
-      <c r="AD8" s="0" t="n">
+      <c r="AD8" s="3" t="n">
         <v>1.8124</v>
       </c>
-      <c r="AE8" s="0" t="n">
+      <c r="AE8" s="3" t="n">
         <v>1.853</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L9" s="0" t="n">
+      <c r="L9" s="3" t="n">
         <v>5.25</v>
       </c>
-      <c r="M9" s="0" t="n">
+      <c r="M9" s="3" t="n">
         <v>1.6504</v>
       </c>
-      <c r="N9" s="0" t="n">
+      <c r="N9" s="3" t="n">
         <v>1.7732</v>
       </c>
-      <c r="O9" s="0" t="n">
+      <c r="O9" s="3" t="n">
         <v>1.7776</v>
       </c>
-      <c r="P9" s="0" t="n">
+      <c r="P9" s="3" t="n">
         <v>1.866</v>
       </c>
-      <c r="Q9" s="0" t="n">
+      <c r="Q9" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="R9" s="0" t="n">
+      <c r="R9" s="3" t="n">
         <v>1.7469</v>
       </c>
-      <c r="S9" s="0" t="n">
+      <c r="S9" s="3" t="n">
         <v>1.8356</v>
       </c>
-      <c r="T9" s="0" t="n">
+      <c r="T9" s="3" t="n">
         <v>1.7691</v>
       </c>
-      <c r="U9" s="0" t="n">
+      <c r="U9" s="3" t="n">
         <v>1.8489</v>
       </c>
-      <c r="V9" s="0" t="n">
+      <c r="V9" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="W9" s="0" t="n">
+      <c r="W9" s="3" t="n">
         <v>1.7299</v>
       </c>
-      <c r="X9" s="0" t="n">
+      <c r="X9" s="3" t="n">
         <v>1.7986</v>
       </c>
-      <c r="Y9" s="0" t="n">
+      <c r="Y9" s="3" t="n">
         <v>1.8036</v>
       </c>
-      <c r="Z9" s="0" t="n">
+      <c r="Z9" s="3" t="n">
         <v>1.8629</v>
       </c>
-      <c r="AA9" s="0" t="n">
+      <c r="AA9" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AB9" s="0" t="n">
+      <c r="AB9" s="3" t="n">
         <v>1.7628</v>
       </c>
-      <c r="AC9" s="0" t="n">
+      <c r="AC9" s="3" t="n">
         <v>1.8161</v>
       </c>
-      <c r="AD9" s="0" t="n">
+      <c r="AD9" s="3" t="n">
         <v>1.798</v>
       </c>
-      <c r="AE9" s="0" t="n">
+      <c r="AE9" s="3" t="n">
         <v>1.8447</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L10" s="0" t="n">
+      <c r="L10" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="M10" s="0" t="n">
+      <c r="M10" s="3" t="n">
         <v>1.6344</v>
       </c>
-      <c r="N10" s="0" t="n">
+      <c r="N10" s="3" t="n">
         <v>1.7988</v>
       </c>
-      <c r="O10" s="0" t="n">
+      <c r="O10" s="3" t="n">
         <v>1.7197</v>
       </c>
-      <c r="P10" s="0" t="n">
+      <c r="P10" s="3" t="n">
         <v>1.8687</v>
       </c>
-      <c r="Q10" s="0" t="n">
+      <c r="Q10" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="R10" s="0" t="n">
+      <c r="R10" s="3" t="n">
         <v>1.7686</v>
       </c>
-      <c r="S10" s="0" t="n">
+      <c r="S10" s="3" t="n">
         <v>1.8327</v>
       </c>
-      <c r="T10" s="0" t="n">
+      <c r="T10" s="3" t="n">
         <v>1.7771</v>
       </c>
-      <c r="U10" s="0" t="n">
+      <c r="U10" s="3" t="n">
         <v>1.8388</v>
       </c>
-      <c r="V10" s="0" t="n">
+      <c r="V10" s="3" t="n">
         <v>7.5</v>
       </c>
-      <c r="W10" s="0" t="n">
+      <c r="W10" s="3" t="n">
         <v>1.7416</v>
       </c>
-      <c r="X10" s="0" t="n">
+      <c r="X10" s="3" t="n">
         <v>1.8182</v>
       </c>
-      <c r="Y10" s="0" t="n">
+      <c r="Y10" s="3" t="n">
         <v>1.7904</v>
       </c>
-      <c r="Z10" s="0" t="n">
+      <c r="Z10" s="3" t="n">
         <v>1.8544</v>
       </c>
-      <c r="AA10" s="0" t="n">
+      <c r="AA10" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="AB10" s="0" t="n">
+      <c r="AB10" s="3" t="n">
         <v>1.7684</v>
       </c>
-      <c r="AC10" s="0" t="n">
+      <c r="AC10" s="3" t="n">
         <v>1.8208</v>
       </c>
-      <c r="AD10" s="0" t="n">
+      <c r="AD10" s="3" t="n">
         <v>1.7939</v>
       </c>
-      <c r="AE10" s="0" t="n">
+      <c r="AE10" s="3" t="n">
         <v>1.8408</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L11" s="0" t="n">
+      <c r="L11" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="M11" s="0" t="n">
+      <c r="M11" s="3" t="n">
         <v>1.638</v>
       </c>
-      <c r="N11" s="0" t="n">
+      <c r="N11" s="3" t="n">
         <v>1.8322</v>
       </c>
-      <c r="O11" s="0" t="n">
+      <c r="O11" s="3" t="n">
         <v>1.7228</v>
       </c>
-      <c r="P11" s="0" t="n">
+      <c r="P11" s="3" t="n">
         <v>1.8696</v>
       </c>
-      <c r="Q11" s="0" t="n">
+      <c r="Q11" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="R11" s="0" t="n">
+      <c r="R11" s="3" t="n">
         <v>1.7846</v>
       </c>
-      <c r="S11" s="0" t="n">
+      <c r="S11" s="3" t="n">
         <v>1.8284</v>
       </c>
-      <c r="T11" s="0" t="n">
+      <c r="T11" s="3" t="n">
         <v>1.7865</v>
       </c>
-      <c r="U11" s="0" t="n">
+      <c r="U11" s="3" t="n">
         <v>1.8297</v>
       </c>
-      <c r="V11" s="0" t="n">
+      <c r="V11" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="W11" s="0" t="n">
+      <c r="W11" s="3" t="n">
         <v>1.7461</v>
       </c>
-      <c r="X11" s="0" t="n">
+      <c r="X11" s="3" t="n">
         <v>1.8222</v>
       </c>
-      <c r="Y11" s="0" t="n">
+      <c r="Y11" s="3" t="n">
         <v>1.7877</v>
       </c>
-      <c r="Z11" s="0" t="n">
+      <c r="Z11" s="3" t="n">
         <v>1.8518</v>
       </c>
-      <c r="AA11" s="0" t="n">
+      <c r="AA11" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="AB11" s="0" t="n">
+      <c r="AB11" s="3" t="n">
         <v>1.7739</v>
       </c>
-      <c r="AC11" s="0" t="n">
+      <c r="AC11" s="3" t="n">
         <v>1.8233</v>
       </c>
-      <c r="AD11" s="0" t="n">
+      <c r="AD11" s="3" t="n">
         <v>1.7918</v>
       </c>
-      <c r="AE11" s="0" t="n">
+      <c r="AE11" s="3" t="n">
         <v>1.8372</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L12" s="0" t="n">
+      <c r="L12" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="M12" s="0" t="n">
+      <c r="M12" s="3" t="n">
         <v>1.6972</v>
       </c>
-      <c r="N12" s="0" t="n">
+      <c r="N12" s="3" t="n">
         <v>1.8331</v>
       </c>
-      <c r="O12" s="0" t="n">
+      <c r="O12" s="3" t="n">
         <v>1.7503</v>
       </c>
-      <c r="P12" s="0" t="n">
+      <c r="P12" s="3" t="n">
         <v>1.8623</v>
       </c>
-      <c r="Q12" s="0" t="n">
+      <c r="Q12" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="R12" s="0" t="n">
+      <c r="R12" s="3" t="n">
         <v>1.7939</v>
       </c>
-      <c r="S12" s="0" t="n">
+      <c r="S12" s="3" t="n">
         <v>1.8241</v>
       </c>
-      <c r="T12" s="0" t="n">
+      <c r="T12" s="3" t="n">
         <v>1.7929</v>
       </c>
-      <c r="U12" s="0" t="n">
+      <c r="U12" s="3" t="n">
         <v>1.8232</v>
       </c>
-      <c r="V12" s="0" t="n">
+      <c r="V12" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="W12" s="0" t="n">
+      <c r="W12" s="3" t="n">
         <v>1.7631</v>
       </c>
-      <c r="X12" s="0" t="n">
+      <c r="X12" s="3" t="n">
         <v>1.829</v>
       </c>
-      <c r="Y12" s="0" t="n">
+      <c r="Y12" s="3" t="n">
         <v>1.7828</v>
       </c>
-      <c r="Z12" s="0" t="n">
+      <c r="Z12" s="3" t="n">
         <v>1.8426</v>
       </c>
-      <c r="AA12" s="0" t="n">
+      <c r="AA12" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="AB12" s="0" t="n">
+      <c r="AB12" s="3" t="n">
         <v>1.7838</v>
       </c>
-      <c r="AC12" s="0" t="n">
+      <c r="AC12" s="3" t="n">
         <v>1.8242</v>
       </c>
-      <c r="AD12" s="0" t="n">
+      <c r="AD12" s="3" t="n">
         <v>1.7915</v>
       </c>
-      <c r="AE12" s="0" t="n">
+      <c r="AE12" s="3" t="n">
         <v>1.8306</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L13" s="0" t="n">
+      <c r="L13" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="M13" s="0" t="n">
+      <c r="M13" s="3" t="n">
         <v>1.7356</v>
       </c>
-      <c r="N13" s="0" t="n">
+      <c r="N13" s="3" t="n">
         <v>1.8385</v>
       </c>
-      <c r="O13" s="0" t="n">
+      <c r="O13" s="3" t="n">
         <v>1.7593</v>
       </c>
-      <c r="P13" s="0" t="n">
+      <c r="P13" s="3" t="n">
         <v>1.8523</v>
       </c>
-      <c r="Q13" s="0" t="n">
+      <c r="Q13" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="R13" s="0" t="n">
+      <c r="R13" s="3" t="n">
         <v>1.7992</v>
       </c>
-      <c r="S13" s="0" t="n">
+      <c r="S13" s="3" t="n">
         <v>1.8207</v>
       </c>
-      <c r="T13" s="0" t="n">
+      <c r="T13" s="3" t="n">
         <v>1.7972</v>
       </c>
-      <c r="U13" s="0" t="n">
+      <c r="U13" s="3" t="n">
         <v>1.8189</v>
       </c>
-      <c r="V13" s="0" t="n">
+      <c r="V13" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="W13" s="0" t="n">
+      <c r="W13" s="3" t="n">
         <v>1.7776</v>
       </c>
-      <c r="X13" s="0" t="n">
+      <c r="X13" s="3" t="n">
         <v>1.8283</v>
       </c>
-      <c r="Y13" s="0" t="n">
+      <c r="Y13" s="3" t="n">
         <v>1.7853</v>
       </c>
-      <c r="Z13" s="0" t="n">
+      <c r="Z13" s="3" t="n">
         <v>1.8344</v>
       </c>
-      <c r="AA13" s="0" t="n">
+      <c r="AA13" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="AB13" s="0" t="n">
+      <c r="AB13" s="3" t="n">
         <v>1.7916</v>
       </c>
-      <c r="AC13" s="0" t="n">
+      <c r="AC13" s="3" t="n">
         <v>1.8228</v>
       </c>
-      <c r="AD13" s="0" t="n">
+      <c r="AD13" s="3" t="n">
         <v>1.794</v>
       </c>
-      <c r="AE13" s="0" t="n">
+      <c r="AE13" s="3" t="n">
         <v>1.825</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L14" s="0" t="n">
+      <c r="L14" s="3" t="n">
         <v>10.5</v>
       </c>
-      <c r="M14" s="0" t="n">
+      <c r="M14" s="3" t="n">
         <v>1.7423</v>
       </c>
-      <c r="N14" s="0" t="n">
+      <c r="N14" s="3" t="n">
         <v>1.8374</v>
       </c>
-      <c r="O14" s="0" t="n">
+      <c r="O14" s="3" t="n">
         <v>1.761</v>
       </c>
-      <c r="P14" s="0" t="n">
+      <c r="P14" s="3" t="n">
         <v>1.8495</v>
       </c>
-      <c r="V14" s="0" t="n">
+      <c r="V14" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="W14" s="0" t="n">
+      <c r="W14" s="3" t="n">
         <v>1.7885</v>
       </c>
-      <c r="X14" s="0" t="n">
+      <c r="X14" s="3" t="n">
         <v>1.8255</v>
       </c>
-      <c r="Y14" s="0" t="n">
+      <c r="Y14" s="3" t="n">
         <v>1.7905</v>
       </c>
-      <c r="Z14" s="0" t="n">
+      <c r="Z14" s="3" t="n">
         <v>1.8273</v>
       </c>
-      <c r="AA14" s="0" t="n">
+      <c r="AA14" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="AB14" s="0" t="n">
+      <c r="AB14" s="3" t="n">
         <v>1.797</v>
       </c>
-      <c r="AC14" s="0" t="n">
+      <c r="AC14" s="3" t="n">
         <v>1.8206</v>
       </c>
-      <c r="AD14" s="0" t="n">
+      <c r="AD14" s="3" t="n">
         <v>1.797</v>
       </c>
-      <c r="AE14" s="0" t="n">
+      <c r="AE14" s="3" t="n">
         <v>1.8207</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L15" s="0" t="n">
+      <c r="L15" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="M15" s="0" t="n">
+      <c r="M15" s="3" t="n">
         <v>1.7625</v>
       </c>
-      <c r="N15" s="0" t="n">
+      <c r="N15" s="3" t="n">
         <v>1.8348</v>
       </c>
-      <c r="O15" s="0" t="n">
+      <c r="O15" s="3" t="n">
         <v>1.7718</v>
       </c>
-      <c r="P15" s="0" t="n">
+      <c r="P15" s="3" t="n">
         <v>1.8414</v>
       </c>
-      <c r="V15" s="0" t="n">
+      <c r="V15" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="W15" s="0" t="n">
+      <c r="W15" s="3" t="n">
         <v>1.7924</v>
       </c>
-      <c r="X15" s="0" t="n">
+      <c r="X15" s="3" t="n">
         <v>1.8239</v>
       </c>
-      <c r="Y15" s="0" t="n">
+      <c r="Y15" s="3" t="n">
         <v>1.7929</v>
       </c>
-      <c r="Z15" s="0" t="n">
+      <c r="Z15" s="3" t="n">
         <v>1.8244</v>
       </c>
-      <c r="AA15" s="0" t="n">
+      <c r="AA15" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="AB15" s="0" t="n">
+      <c r="AB15" s="3" t="n">
         <v>1.8007</v>
       </c>
-      <c r="AC15" s="0" t="n">
+      <c r="AC15" s="3" t="n">
         <v>1.8185</v>
       </c>
-      <c r="AD15" s="0" t="n">
+      <c r="AD15" s="3" t="n">
         <v>1.7995</v>
       </c>
-      <c r="AE15" s="0" t="n">
+      <c r="AE15" s="3" t="n">
         <v>1.8176</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L16" s="0" t="n">
+      <c r="L16" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="M16" s="0" t="n">
+      <c r="M16" s="3" t="n">
         <v>1.7823</v>
       </c>
-      <c r="N16" s="0" t="n">
+      <c r="N16" s="3" t="n">
         <v>1.8299</v>
       </c>
-      <c r="O16" s="0" t="n">
+      <c r="O16" s="3" t="n">
         <v>1.7844</v>
       </c>
-      <c r="P16" s="0" t="n">
+      <c r="P16" s="3" t="n">
         <v>1.8309</v>
       </c>
-      <c r="V16" s="0" t="n">
+      <c r="V16" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="W16" s="0" t="n">
+      <c r="W16" s="3" t="n">
         <v>1.7955</v>
       </c>
-      <c r="X16" s="0" t="n">
+      <c r="X16" s="3" t="n">
         <v>1.8223</v>
       </c>
-      <c r="Y16" s="0" t="n">
+      <c r="Y16" s="3" t="n">
         <v>1.795</v>
       </c>
-      <c r="Z16" s="0" t="n">
+      <c r="Z16" s="3" t="n">
         <v>1.8219</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L17" s="0" t="n">
+      <c r="L17" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="M17" s="0" t="n">
+      <c r="M17" s="3" t="n">
         <v>1.793</v>
       </c>
-      <c r="N17" s="0" t="n">
+      <c r="N17" s="3" t="n">
         <v>1.8249</v>
       </c>
-      <c r="O17" s="0" t="n">
+      <c r="O17" s="3" t="n">
         <v>1.7919</v>
       </c>
-      <c r="P17" s="0" t="n">
+      <c r="P17" s="3" t="n">
         <v>1.8238</v>
       </c>
-      <c r="V17" s="0" t="n">
+      <c r="V17" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="W17" s="0" t="n">
+      <c r="W17" s="3" t="n">
         <v>1.7999</v>
       </c>
-      <c r="X17" s="0" t="n">
+      <c r="X17" s="3" t="n">
         <v>1.8196</v>
       </c>
-      <c r="Y17" s="0" t="n">
+      <c r="Y17" s="3" t="n">
         <v>1.7983</v>
       </c>
-      <c r="Z17" s="0" t="n">
+      <c r="Z17" s="3" t="n">
         <v>1.8183</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L18" s="0" t="n">
+      <c r="L18" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="M18" s="0" t="n">
+      <c r="M18" s="3" t="n">
         <v>1.7988</v>
       </c>
-      <c r="N18" s="0" t="n">
+      <c r="N18" s="3" t="n">
         <v>1.8211</v>
       </c>
-      <c r="O18" s="0" t="n">
+      <c r="O18" s="3" t="n">
         <v>1.7967</v>
       </c>
-      <c r="P18" s="0" t="n">
+      <c r="P18" s="3" t="n">
         <v>1.8192</v>
       </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Обычный"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Обычный"&amp;12Страница &amp;P</oddFooter>
@@ -2714,46 +2839,46 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AB21"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="I2" s="0" t="s">
+      <c r="I2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="0" t="s">
+      <c r="J2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="P2" s="0" t="s">
+      <c r="P2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="Q2" s="0" t="s">
+      <c r="Q2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="W2" s="0" t="s">
+      <c r="W2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="X2" s="0" t="s">
+      <c r="X2" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="3" t="n">
         <v>1.5</v>
       </c>
       <c r="C3" s="2" t="n">
@@ -2762,16 +2887,16 @@
       <c r="D3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="F3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="0" t="s">
+      <c r="G3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="0" t="n">
+      <c r="I3" s="3" t="n">
         <v>1.75</v>
       </c>
       <c r="J3" s="2" t="n">
@@ -2780,13 +2905,13 @@
       <c r="K3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="L3" s="0" t="s">
+      <c r="L3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M3" s="0" t="s">
+      <c r="M3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N3" s="0" t="s">
+      <c r="N3" s="3" t="s">
         <v>18</v>
       </c>
       <c r="P3" s="2" t="n">
@@ -2798,16 +2923,16 @@
       <c r="R3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S3" s="0" t="s">
+      <c r="S3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T3" s="0" t="s">
+      <c r="T3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="U3" s="0" t="s">
+      <c r="U3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="W3" s="0" t="n">
+      <c r="W3" s="3" t="n">
         <v>2.25</v>
       </c>
       <c r="X3" s="2" t="n">
@@ -2816,605 +2941,634 @@
       <c r="Y3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Z3" s="0" t="s">
+      <c r="Z3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AA3" s="0" t="s">
+      <c r="AA3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="AB3" s="0" t="s">
+      <c r="AB3" s="3" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="J4" s="0" t="s">
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="J4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
-      <c r="Q4" s="0" t="s">
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+      <c r="Q4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="S4" s="4"/>
-      <c r="T4" s="4"/>
-      <c r="X4" s="0" t="s">
+      <c r="S4" s="5"/>
+      <c r="T4" s="5"/>
+      <c r="X4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="Z4" s="4"/>
-      <c r="AA4" s="4"/>
+      <c r="Z4" s="5"/>
+      <c r="AA4" s="5"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C5" s="0" t="n">
+      <c r="C5" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="D5" s="3" t="n">
         <v>0.4828</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="E5" s="7" t="n">
         <v>1.8094</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F5" s="7" t="n">
         <v>1.8094</v>
       </c>
-      <c r="G5" s="0" t="n">
+      <c r="G5" s="3" t="n">
         <v>0.4828</v>
       </c>
-      <c r="I5" s="0" t="n">
+      <c r="I5" s="3" t="n">
         <f aca="false">COS(3.14159265359/(J5+1))</f>
         <v>-1.03411553555107E-013</v>
       </c>
-      <c r="J5" s="0" t="n">
+      <c r="J5" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="K5" s="0" t="n">
+      <c r="K5" s="3" t="n">
         <v>0.4828</v>
       </c>
-      <c r="L5" s="6" t="n">
+      <c r="L5" s="7" t="n">
         <v>1.8094</v>
       </c>
-      <c r="M5" s="6" t="n">
+      <c r="M5" s="7" t="n">
         <v>1.8094</v>
       </c>
-      <c r="N5" s="0" t="n">
+      <c r="N5" s="3" t="n">
         <v>0.4828</v>
       </c>
-      <c r="P5" s="0" t="n">
+      <c r="P5" s="3" t="n">
         <f aca="false">COS(3.14159265359/(Q5+1))</f>
         <v>-1.03411553555107E-013</v>
       </c>
-      <c r="Q5" s="0" t="n">
+      <c r="Q5" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="R5" s="0" t="n">
+      <c r="R5" s="3" t="n">
         <v>0.4828</v>
       </c>
-      <c r="S5" s="6" t="n">
+      <c r="S5" s="7" t="n">
         <v>1.8094</v>
       </c>
-      <c r="T5" s="6" t="n">
+      <c r="T5" s="7" t="n">
         <v>1.8094</v>
       </c>
-      <c r="U5" s="0" t="n">
+      <c r="U5" s="3" t="n">
         <v>0.4828</v>
       </c>
-      <c r="W5" s="0" t="n">
+      <c r="W5" s="3" t="n">
         <f aca="false">COS(3.14159265359/(X5+1))</f>
         <v>-1.03411553555107E-013</v>
       </c>
-      <c r="X5" s="0" t="n">
+      <c r="X5" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="Y5" s="0" t="n">
+      <c r="Y5" s="3" t="n">
         <v>0.4828</v>
       </c>
-      <c r="Z5" s="6" t="n">
+      <c r="Z5" s="7" t="n">
         <v>1.8094</v>
       </c>
-      <c r="AA5" s="6" t="n">
+      <c r="AA5" s="7" t="n">
         <v>1.8094</v>
       </c>
-      <c r="AB5" s="0" t="n">
+      <c r="AB5" s="3" t="n">
         <v>0.4828</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C6" s="0" t="n">
+      <c r="C6" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="I6" s="0" t="n">
+      <c r="I6" s="3" t="n">
         <f aca="false">COS(3.14159265359/(J6+1))</f>
         <v>0.49999999999994</v>
       </c>
-      <c r="J6" s="0" t="n">
+      <c r="J6" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="K6" s="0" t="n">
+      <c r="K6" s="3" t="n">
         <v>0.6378</v>
       </c>
-      <c r="L6" s="0" t="n">
+      <c r="L6" s="3" t="n">
         <v>1.8408</v>
       </c>
-      <c r="M6" s="0" t="n">
+      <c r="M6" s="3" t="n">
         <v>1.8749</v>
       </c>
-      <c r="N6" s="0" t="n">
+      <c r="N6" s="3" t="n">
         <v>0.6546</v>
       </c>
-      <c r="P6" s="0" t="n">
+      <c r="P6" s="3" t="n">
         <f aca="false">COS(3.14159265359/(Q6+1))</f>
         <v>0.49999999999994</v>
       </c>
-      <c r="Q6" s="0" t="n">
+      <c r="Q6" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="R6" s="0" t="n">
+      <c r="R6" s="3" t="n">
         <v>0.635</v>
       </c>
-      <c r="S6" s="0" t="n">
+      <c r="S6" s="3" t="n">
         <v>1.8226</v>
       </c>
-      <c r="T6" s="0" t="n">
+      <c r="T6" s="3" t="n">
         <v>1.8811</v>
       </c>
-      <c r="U6" s="0" t="n">
+      <c r="U6" s="3" t="n">
         <v>0.6671</v>
       </c>
-      <c r="W6" s="0" t="n">
+      <c r="W6" s="3" t="n">
         <f aca="false">COS(3.14159265359/(X6+1))</f>
         <v>0.49999999999994</v>
       </c>
-      <c r="X6" s="0" t="n">
+      <c r="X6" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Y6" s="0" t="n">
+      <c r="Y6" s="3" t="n">
         <v>0.6413</v>
       </c>
-      <c r="Z6" s="0" t="n">
+      <c r="Z6" s="3" t="n">
         <v>1.8087</v>
       </c>
-      <c r="AA6" s="0" t="n">
+      <c r="AA6" s="3" t="n">
         <v>1.8879</v>
       </c>
-      <c r="AB6" s="0" t="n">
+      <c r="AB6" s="3" t="n">
         <v>0.6832</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C7" s="0" t="n">
+      <c r="C7" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="I7" s="0" t="n">
+      <c r="I7" s="3" t="n">
         <f aca="false">COS(3.14159265359/(J7+1))</f>
         <v>0.707106781186511</v>
       </c>
-      <c r="J7" s="0" t="n">
+      <c r="J7" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="K7" s="0" t="n">
+      <c r="K7" s="3" t="n">
         <v>0.7846</v>
       </c>
-      <c r="L7" s="0" t="n">
+      <c r="L7" s="3" t="n">
         <v>1.857</v>
       </c>
-      <c r="M7" s="0" t="n">
+      <c r="M7" s="3" t="n">
         <v>1.904</v>
       </c>
-      <c r="N7" s="0" t="n">
+      <c r="N7" s="3" t="n">
         <v>0.7947</v>
       </c>
-      <c r="P7" s="0" t="n">
+      <c r="P7" s="3" t="n">
         <f aca="false">COS(3.14159265359/(Q7+1))</f>
         <v>0.707106781186511</v>
       </c>
-      <c r="Q7" s="0" t="n">
+      <c r="Q7" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="R7" s="0" t="n">
+      <c r="R7" s="3" t="n">
         <v>0.7877</v>
       </c>
-      <c r="S7" s="0" t="n">
+      <c r="S7" s="3" t="n">
         <v>1.8307</v>
       </c>
-      <c r="T7" s="0" t="n">
+      <c r="T7" s="3" t="n">
         <v>1.9118</v>
       </c>
-      <c r="U7" s="0" t="n">
+      <c r="U7" s="3" t="n">
         <v>0.8213</v>
       </c>
-      <c r="W7" s="0" t="n">
+      <c r="W7" s="3" t="n">
         <f aca="false">COS(3.14159265359/(X7+1))</f>
         <v>0.707106781186511</v>
       </c>
-      <c r="X7" s="0" t="n">
+      <c r="X7" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="Y7" s="0" t="n">
+      <c r="Y7" s="3" t="n">
         <v>0.804</v>
       </c>
-      <c r="Z7" s="0" t="n">
+      <c r="Z7" s="3" t="n">
         <v>1.8096</v>
       </c>
-      <c r="AA7" s="0" t="n">
+      <c r="AA7" s="3" t="n">
         <v>1.9208</v>
       </c>
-      <c r="AB7" s="0" t="n">
+      <c r="AB7" s="3" t="n">
         <v>0.8498</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C8" s="0" t="n">
+      <c r="C8" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="I8" s="0" t="n">
+      <c r="I8" s="3" t="n">
         <f aca="false">COS(3.14159265359/(J8+1))</f>
         <v>0.809016994374923</v>
       </c>
-      <c r="J8" s="0" t="n">
+      <c r="J8" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="K8" s="0" t="n">
+      <c r="K8" s="3" t="n">
         <v>0.9272</v>
       </c>
-      <c r="L8" s="0" t="n">
+      <c r="L8" s="3" t="n">
         <v>1.8661</v>
       </c>
-      <c r="M8" s="0" t="n">
+      <c r="M8" s="3" t="n">
         <v>1.92</v>
       </c>
-      <c r="N8" s="0" t="n">
+      <c r="N8" s="3" t="n">
         <v>0.9283</v>
       </c>
-      <c r="P8" s="0" t="n">
+      <c r="P8" s="3" t="n">
         <f aca="false">COS(3.14159265359/(Q8+1))</f>
         <v>0.809016994374923</v>
       </c>
-      <c r="Q8" s="0" t="n">
+      <c r="Q8" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="R8" s="0" t="n">
+      <c r="R8" s="3" t="n">
         <v>0.941</v>
       </c>
-      <c r="S8" s="0" t="n">
+      <c r="S8" s="3" t="n">
         <v>1.8352</v>
       </c>
-      <c r="T8" s="0" t="n">
+      <c r="T8" s="3" t="n">
         <v>1.9289</v>
       </c>
-      <c r="U8" s="0" t="n">
+      <c r="U8" s="3" t="n">
         <v>0.9682</v>
       </c>
-      <c r="W8" s="0" t="n">
+      <c r="W8" s="3" t="n">
         <f aca="false">COS(3.14159265359/(X8+1))</f>
         <v>0.809016994374923</v>
       </c>
-      <c r="X8" s="0" t="n">
+      <c r="X8" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="Y8" s="0" t="n">
+      <c r="Y8" s="3" t="n">
         <v>0.9754</v>
       </c>
-      <c r="Z8" s="0" t="n">
+      <c r="Z8" s="3" t="n">
         <v>1.8102</v>
       </c>
-      <c r="AA8" s="0" t="n">
+      <c r="AA8" s="3" t="n">
         <v>1.9392</v>
       </c>
-      <c r="AB8" s="0" t="n">
+      <c r="AB8" s="3" t="n">
         <v>1.0068</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P9" s="0" t="n">
+      <c r="P9" s="3" t="n">
         <f aca="false">COS(3.14159265359/(Q9+1))</f>
         <v>0.866025403784421</v>
       </c>
-      <c r="Q9" s="0" t="n">
+      <c r="Q9" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="R9" s="0" t="n">
+      <c r="R9" s="3" t="n">
         <v>1.0974</v>
       </c>
-      <c r="S9" s="0" t="n">
+      <c r="S9" s="3" t="n">
         <v>1.8383</v>
       </c>
-      <c r="T9" s="0" t="n">
+      <c r="T9" s="3" t="n">
         <v>1.9399</v>
       </c>
-      <c r="U9" s="0" t="n">
+      <c r="U9" s="3" t="n">
         <v>1.1062</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L10" s="7" t="n">
+      <c r="L10" s="8" t="n">
         <v>1.8776</v>
       </c>
-      <c r="M10" s="7" t="n">
+      <c r="M10" s="8" t="n">
         <v>1.9444</v>
       </c>
-      <c r="S10" s="8" t="n">
+      <c r="S10" s="9" t="n">
         <v>1.84</v>
       </c>
-      <c r="T10" s="8" t="n">
+      <c r="T10" s="9" t="n">
         <v>1.9554</v>
       </c>
-      <c r="Z10" s="7" t="n">
+      <c r="Z10" s="8" t="n">
         <v>1.8111</v>
       </c>
-      <c r="AA10" s="7" t="n">
+      <c r="AA10" s="8" t="n">
         <v>1.9684</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="3" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="0" t="s">
+      <c r="C13" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D13" s="0" t="s">
+      <c r="D13" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E13" s="0" t="s">
+      <c r="E13" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F13" s="0" t="s">
+      <c r="F13" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="G13" s="0" t="s">
+      <c r="G13" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="P13" s="0" t="s">
+      <c r="P13" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="Q13" s="0" t="s">
+      <c r="Q13" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="n">
+      <c r="A14" s="3" t="n">
         <v>0.185</v>
       </c>
-      <c r="B14" s="0" t="n">
+      <c r="B14" s="3" t="n">
         <v>3.632</v>
       </c>
-      <c r="C14" s="0" t="n">
+      <c r="C14" s="3" t="n">
         <v>3.214</v>
       </c>
       <c r="P14" s="2" t="n">
         <v>1.9</v>
       </c>
-      <c r="Q14" s="9" t="n">
+      <c r="Q14" s="10" t="n">
         <v>3.35</v>
       </c>
       <c r="R14" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S14" s="0" t="s">
+      <c r="S14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T14" s="0" t="s">
+      <c r="T14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="U14" s="0" t="s">
+      <c r="U14" s="3" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C15" s="0" t="s">
+      <c r="C15" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="Q15" s="0" t="s">
+      <c r="Q15" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="S15" s="4"/>
-      <c r="T15" s="4"/>
+      <c r="S15" s="5"/>
+      <c r="T15" s="5"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="0" t="n">
+      <c r="B16" s="3" t="n">
         <f aca="false">COS(3.14159265359/(C16+1))</f>
         <v>-1.03411553555107E-013</v>
       </c>
-      <c r="C16" s="0" t="n">
+      <c r="C16" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="0" t="n">
+      <c r="D16" s="3" t="n">
         <v>0.4828</v>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="E16" s="7" t="n">
         <v>1.8094</v>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="F16" s="7" t="n">
         <v>1.8094</v>
       </c>
-      <c r="G16" s="0" t="n">
+      <c r="G16" s="3" t="n">
         <v>0.4828</v>
       </c>
-      <c r="P16" s="0" t="n">
+      <c r="P16" s="3" t="n">
         <f aca="false">COS(3.14159265359/(Q16+1))</f>
         <v>-1.03411553555107E-013</v>
       </c>
-      <c r="Q16" s="0" t="n">
+      <c r="Q16" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="R16" s="0" t="n">
+      <c r="R16" s="3" t="n">
         <v>0.4828</v>
       </c>
-      <c r="S16" s="6" t="n">
+      <c r="S16" s="7" t="n">
         <v>1.8094</v>
       </c>
-      <c r="T16" s="6" t="n">
+      <c r="T16" s="7" t="n">
         <v>1.8094</v>
       </c>
-      <c r="U16" s="0" t="n">
+      <c r="U16" s="3" t="n">
         <v>0.4828</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="0" t="n">
+      <c r="B17" s="3" t="n">
         <f aca="false">COS(3.14159265359/(C17+1))</f>
         <v>0.49999999999994</v>
       </c>
-      <c r="C17" s="0" t="n">
+      <c r="C17" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D17" s="0" t="n">
+      <c r="D17" s="3" t="n">
         <v>0.7147</v>
       </c>
-      <c r="E17" s="0" t="n">
+      <c r="E17" s="3" t="n">
         <v>1.7655</v>
       </c>
-      <c r="F17" s="0" t="n">
+      <c r="F17" s="3" t="n">
         <v>1.8869</v>
       </c>
-      <c r="G17" s="0" t="n">
+      <c r="G17" s="3" t="n">
         <v>0.6963</v>
       </c>
-      <c r="P17" s="0" t="n">
+      <c r="P17" s="3" t="n">
         <f aca="false">COS(3.14159265359/(Q17+1))</f>
         <v>0.49999999999994</v>
       </c>
-      <c r="Q17" s="0" t="n">
+      <c r="Q17" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="R17" s="0" t="n">
+      <c r="R17" s="3" t="n">
         <v>0.5833</v>
       </c>
-      <c r="S17" s="0" t="n">
+      <c r="S17" s="3" t="n">
         <v>1.7973</v>
       </c>
-      <c r="T17" s="0" t="n">
+      <c r="T17" s="3" t="n">
         <v>1.8666</v>
       </c>
-      <c r="U17" s="0" t="n">
+      <c r="U17" s="3" t="n">
         <v>0.632</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="0" t="n">
+      <c r="B18" s="3" t="n">
         <f aca="false">COS(3.14159265359/(C18+1))</f>
         <v>0.707106781186511</v>
       </c>
-      <c r="C18" s="0" t="n">
+      <c r="C18" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D18" s="0" t="n">
+      <c r="D18" s="3" t="n">
         <v>0.9987</v>
       </c>
-      <c r="E18" s="0" t="n">
+      <c r="E18" s="3" t="n">
         <v>1.7502</v>
       </c>
-      <c r="F18" s="0" t="n">
+      <c r="F18" s="3" t="n">
         <v>1.9206</v>
       </c>
-      <c r="G18" s="0" t="n">
+      <c r="G18" s="3" t="n">
         <v>0.8711</v>
       </c>
-      <c r="P18" s="0" t="n">
+      <c r="P18" s="3" t="n">
         <f aca="false">COS(3.14159265359/(Q18+1))</f>
         <v>0.707106781186511</v>
       </c>
-      <c r="Q18" s="0" t="n">
+      <c r="Q18" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="R18" s="0" t="n">
+      <c r="R18" s="3" t="n">
         <v>0.7073</v>
       </c>
-      <c r="S18" s="0" t="n">
+      <c r="S18" s="3" t="n">
         <v>1.7996</v>
       </c>
-      <c r="T18" s="0" t="n">
+      <c r="T18" s="3" t="n">
         <v>1.8919</v>
       </c>
-      <c r="U18" s="0" t="n">
+      <c r="U18" s="3" t="n">
         <v>0.762</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="0" t="n">
+      <c r="B19" s="3" t="n">
         <f aca="false">COS(3.14159265359/(C19+1))</f>
         <v>0.809016994374923</v>
       </c>
-      <c r="C19" s="0" t="n">
+      <c r="C19" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="D19" s="0" t="n">
+      <c r="D19" s="3" t="n">
         <v>1.2911</v>
       </c>
-      <c r="E19" s="0" t="n">
+      <c r="E19" s="3" t="n">
         <v>1.7404</v>
       </c>
-      <c r="F19" s="0" t="n">
+      <c r="F19" s="3" t="n">
         <v>1.9392</v>
       </c>
-      <c r="G19" s="0" t="n">
+      <c r="G19" s="3" t="n">
         <v>1.0328</v>
       </c>
-      <c r="P19" s="0" t="n">
+      <c r="P19" s="3" t="n">
         <f aca="false">COS(3.14159265359/(Q19+1))</f>
         <v>0.809016994374923</v>
       </c>
-      <c r="Q19" s="0" t="n">
+      <c r="Q19" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="R19" s="0" t="n">
+      <c r="R19" s="3" t="n">
         <v>0.8389</v>
       </c>
-      <c r="S19" s="0" t="n">
+      <c r="S19" s="3" t="n">
         <v>1.801</v>
       </c>
-      <c r="T19" s="0" t="n">
-        <v>1.9289</v>
-      </c>
-      <c r="U19" s="0" t="n">
+      <c r="T19" s="3" t="n">
+        <v>1.9055</v>
+      </c>
+      <c r="U19" s="3" t="n">
         <v>0.8875</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="0" t="n">
+      <c r="B20" s="3" t="n">
         <f aca="false">COS(3.14159265359/(C20+1))</f>
         <v>0.866025403784421</v>
       </c>
-      <c r="C20" s="0" t="n">
+      <c r="C20" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="D20" s="0" t="n">
+      <c r="D20" s="3" t="n">
         <v>1.5205</v>
       </c>
-      <c r="E20" s="0" t="n">
+      <c r="E20" s="3" t="n">
         <v>1.7347</v>
       </c>
-      <c r="F20" s="0" t="n">
+      <c r="F20" s="3" t="n">
         <v>1.951</v>
       </c>
-      <c r="G20" s="0" t="n">
+      <c r="G20" s="3" t="n">
         <v>1.1878</v>
       </c>
+      <c r="R20" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" s="11" t="n">
+        <v>1.9269</v>
+      </c>
+      <c r="U20" s="11" t="n">
+        <v>1.127</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E21" s="7" t="n">
+      <c r="D21" s="11" t="n">
+        <v>1.518</v>
+      </c>
+      <c r="E21" s="8" t="n">
         <v>1.7239</v>
       </c>
-      <c r="F21" s="7" t="n">
+      <c r="F21" s="8" t="n">
         <v>1.97</v>
+      </c>
+      <c r="G21" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" s="12" t="n">
+        <v>1.8031</v>
+      </c>
+      <c r="T21" s="13" t="n">
+        <v>1.9291</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="S22" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="T22" s="12" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Обычный"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Обычный"&amp;12Страница &amp;P</oddFooter>

--- a/exciton.xlsx
+++ b/exciton.xlsx
@@ -8,9 +8,9 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="Лист1" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Лист2" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Лист3" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Лист1" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="Лист2" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="Лист3" sheetId="3" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="28">
   <si>
     <t xml:space="preserve">along N-Zn-N</t>
   </si>
@@ -335,119 +335,13 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
-  <a:themeElements>
-    <a:clrScheme name="LibreOffice">
-      <a:dk1>
-        <a:srgbClr val="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:srgbClr val="ffffff"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="000000"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="ffffff"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="18a303"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="0369a3"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="a33e03"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8e03a3"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="c99c00"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="c9211e"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000ee"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="551a8b"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme>
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter/>
-        </a:ln>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter/>
-        </a:ln>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-</a:theme>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AJ23"/>
-  <sheetFormatPr defaultColWidth="11.89453125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.9140625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -1754,7 +1648,7 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Обычный"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Обычный"&amp;12Страница &amp;P</oddFooter>
@@ -1763,12 +1657,12 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AE18"/>
-  <sheetFormatPr defaultColWidth="11.77734375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.78515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
@@ -2830,7 +2724,7 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Обычный"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Обычный"&amp;12Страница &amp;P</oddFooter>
@@ -2839,12 +2733,12 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AB22"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:AB33"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
@@ -3558,17 +3452,167 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D22" s="12" t="n">
+        <v>1.656</v>
+      </c>
+      <c r="E22" s="12" t="n">
+        <v>1.7244</v>
+      </c>
+      <c r="F22" s="12" t="n">
+        <v>1.9729</v>
+      </c>
       <c r="S22" s="12" t="s">
         <v>27</v>
       </c>
       <c r="T22" s="12" t="s">
         <v>27</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P25" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q25" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P26" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q26" s="2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="T26" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="U26" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q27" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="S27" s="5"/>
+      <c r="T27" s="5"/>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P28" s="3" t="n">
+        <f aca="false">COS(3.14159265359/(Q28+1))</f>
+        <v>-1.03411553555107E-013</v>
+      </c>
+      <c r="Q28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>0.4828</v>
+      </c>
+      <c r="S28" s="7" t="n">
+        <v>1.8094</v>
+      </c>
+      <c r="T28" s="7" t="n">
+        <v>1.8094</v>
+      </c>
+      <c r="U28" s="3" t="n">
+        <v>0.4828</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P29" s="3" t="n">
+        <f aca="false">COS(3.14159265359/(Q29+1))</f>
+        <v>0.49999999999994</v>
+      </c>
+      <c r="Q29" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>0.6016</v>
+      </c>
+      <c r="S29" s="3" t="n">
+        <v>1.8012</v>
+      </c>
+      <c r="T29" s="3" t="n">
+        <v>1.876</v>
+      </c>
+      <c r="U29" s="3" t="n">
+        <v>0.6521</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P30" s="3" t="n">
+        <f aca="false">COS(3.14159265359/(Q30+1))</f>
+        <v>0.707106781186511</v>
+      </c>
+      <c r="Q30" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>0.7364</v>
+      </c>
+      <c r="S30" s="3" t="n">
+        <v>1.8027</v>
+      </c>
+      <c r="T30" s="3" t="n">
+        <v>1.9042</v>
+      </c>
+      <c r="U30" s="3" t="n">
+        <v>0.795</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P31" s="3" t="n">
+        <f aca="false">COS(3.14159265359/(Q31+1))</f>
+        <v>0.809016994374923</v>
+      </c>
+      <c r="Q31" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>0.8772</v>
+      </c>
+      <c r="S31" s="3" t="n">
+        <v>1.8038</v>
+      </c>
+      <c r="T31" s="3" t="n">
+        <v>1.9198</v>
+      </c>
+      <c r="U31" s="3" t="n">
+        <v>0.933</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="S32" s="11" t="n">
+        <v>1.8004</v>
+      </c>
+      <c r="T32" s="11" t="n">
+        <v>1.9446</v>
+      </c>
+      <c r="U32" s="11" t="n">
+        <v>1.133</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="S33" s="12" t="n">
+        <v>1.8053</v>
+      </c>
+      <c r="T33" s="12" t="n">
+        <v>1.9462</v>
+      </c>
+      <c r="U33" s="12" t="n">
+        <v>1.019</v>
       </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Обычный"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Обычный"&amp;12Страница &amp;P</oddFooter>

--- a/exciton.xlsx
+++ b/exciton.xlsx
@@ -8,9 +8,9 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="Лист1" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="Лист2" sheetId="2" state="visible" r:id="rId3"/>
-    <sheet name="Лист3" sheetId="3" state="visible" r:id="rId4"/>
+    <sheet name="Лист1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Лист2" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Лист3" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="28">
   <si>
     <t xml:space="preserve">along N-Zn-N</t>
   </si>
@@ -206,7 +206,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -251,15 +251,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -335,8 +331,114 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="LibreOffice">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="ffffff"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="ffffff"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="18a303"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="0369a3"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="a33e03"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8e03a3"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="c99c00"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="c9211e"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000ee"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="551a8b"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -1648,7 +1750,7 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Обычный"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Обычный"&amp;12Страница &amp;P</oddFooter>
@@ -1657,7 +1759,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -2724,7 +2826,7 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Обычный"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Обычный"&amp;12Страница &amp;P</oddFooter>
@@ -2733,11 +2835,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AB33"/>
+  <dimension ref="A1:AB44"/>
   <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3421,18 +3523,18 @@
       <c r="G20" s="3" t="n">
         <v>1.1878</v>
       </c>
-      <c r="R20" s="11" t="n">
+      <c r="R20" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="T20" s="11" t="n">
+      <c r="T20" s="8" t="n">
         <v>1.9269</v>
       </c>
-      <c r="U20" s="11" t="n">
+      <c r="U20" s="8" t="n">
         <v>1.127</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D21" s="11" t="n">
+      <c r="D21" s="8" t="n">
         <v>1.518</v>
       </c>
       <c r="E21" s="8" t="n">
@@ -3441,30 +3543,30 @@
       <c r="F21" s="8" t="n">
         <v>1.97</v>
       </c>
-      <c r="G21" s="11" t="n">
+      <c r="G21" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="S21" s="12" t="n">
+      <c r="S21" s="9" t="n">
         <v>1.8031</v>
       </c>
-      <c r="T21" s="13" t="n">
+      <c r="T21" s="11" t="n">
         <v>1.9291</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D22" s="12" t="n">
+      <c r="D22" s="9" t="n">
         <v>1.656</v>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="E22" s="9" t="n">
         <v>1.7244</v>
       </c>
-      <c r="F22" s="12" t="n">
+      <c r="F22" s="9" t="n">
         <v>1.9729</v>
       </c>
-      <c r="S22" s="12" t="s">
+      <c r="S22" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="T22" s="12" t="s">
+      <c r="T22" s="9" t="s">
         <v>27</v>
       </c>
     </row>
@@ -3475,6 +3577,12 @@
       <c r="Q25" s="3" t="s">
         <v>1</v>
       </c>
+      <c r="W25" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="X25" s="3" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="P26" s="2" t="n">
@@ -3495,6 +3603,24 @@
       <c r="U26" s="3" t="s">
         <v>18</v>
       </c>
+      <c r="W26" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="X26" s="2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z26" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA26" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="AB26" s="3" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Q27" s="3" t="s">
@@ -3502,6 +3628,11 @@
       </c>
       <c r="S27" s="5"/>
       <c r="T27" s="5"/>
+      <c r="X27" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z27" s="5"/>
+      <c r="AA27" s="5"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="P28" s="3" t="n">
@@ -3523,6 +3654,25 @@
       <c r="U28" s="3" t="n">
         <v>0.4828</v>
       </c>
+      <c r="W28" s="3" t="n">
+        <f aca="false">COS(3.14159265359/(X28+1))</f>
+        <v>-1.03411553555107E-013</v>
+      </c>
+      <c r="X28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y28" s="3" t="n">
+        <v>0.4828</v>
+      </c>
+      <c r="Z28" s="7" t="n">
+        <v>1.8094</v>
+      </c>
+      <c r="AA28" s="7" t="n">
+        <v>1.8094</v>
+      </c>
+      <c r="AB28" s="3" t="n">
+        <v>0.4828</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="P29" s="3" t="n">
@@ -3544,6 +3694,25 @@
       <c r="U29" s="3" t="n">
         <v>0.6521</v>
       </c>
+      <c r="W29" s="3" t="n">
+        <f aca="false">COS(3.14159265359/(X29+1))</f>
+        <v>0.49999999999994</v>
+      </c>
+      <c r="X29" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y29" s="3" t="n">
+        <v>0.5617</v>
+      </c>
+      <c r="Z29" s="3" t="n">
+        <v>1.7723</v>
+      </c>
+      <c r="AA29" s="3" t="n">
+        <v>1.8678</v>
+      </c>
+      <c r="AB29" s="3" t="n">
+        <v>0.631</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="P30" s="3" t="n">
@@ -3565,6 +3734,25 @@
       <c r="U30" s="3" t="n">
         <v>0.795</v>
       </c>
+      <c r="W30" s="3" t="n">
+        <f aca="false">COS(3.14159265359/(X30+1))</f>
+        <v>0.707106781186511</v>
+      </c>
+      <c r="X30" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y30" s="3" t="n">
+        <v>0.6788</v>
+      </c>
+      <c r="Z30" s="3" t="n">
+        <v>1.7666</v>
+      </c>
+      <c r="AA30" s="3" t="n">
+        <v>1.8928</v>
+      </c>
+      <c r="AB30" s="3" t="n">
+        <v>0.7616</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="P31" s="3" t="n">
@@ -3586,33 +3774,320 @@
       <c r="U31" s="3" t="n">
         <v>0.933</v>
       </c>
+      <c r="W31" s="3" t="n">
+        <f aca="false">COS(3.14159265359/(X31+1))</f>
+        <v>0.809016994374923</v>
+      </c>
+      <c r="X31" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y31" s="3" t="n">
+        <v>0.8042</v>
+      </c>
+      <c r="Z31" s="3" t="n">
+        <v>1.7644</v>
+      </c>
+      <c r="AA31" s="3" t="n">
+        <v>1.9069</v>
+      </c>
+      <c r="AB31" s="3" t="n">
+        <v>0.8838</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="S32" s="11" t="n">
+      <c r="R32" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="S32" s="8" t="n">
         <v>1.8004</v>
       </c>
-      <c r="T32" s="11" t="n">
+      <c r="T32" s="8" t="n">
         <v>1.9446</v>
       </c>
-      <c r="U32" s="11" t="n">
+      <c r="U32" s="8" t="n">
         <v>1.133</v>
       </c>
+      <c r="Y32" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z32" s="12" t="n">
+        <v>1.7497</v>
+      </c>
+      <c r="AA32" s="12" t="n">
+        <v>1.9285</v>
+      </c>
+      <c r="AB32" s="12" t="n">
+        <v>1.233</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="S33" s="12" t="n">
+      <c r="S33" s="9" t="n">
         <v>1.8053</v>
       </c>
-      <c r="T33" s="12" t="n">
+      <c r="T33" s="9" t="n">
         <v>1.9462</v>
       </c>
-      <c r="U33" s="12" t="n">
+      <c r="U33" s="9" t="n">
         <v>1.019</v>
+      </c>
+      <c r="Z33" s="0" t="n">
+        <v>1.7593</v>
+      </c>
+      <c r="AA33" s="0" t="n">
+        <v>1.9304</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P37" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q37" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="W37" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="X37" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P38" s="10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q38" s="2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R38" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="S38" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="T38" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="U38" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W38" s="10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="X38" s="2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y38" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z38" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA38" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="AB38" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q39" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="S39" s="5"/>
+      <c r="T39" s="5"/>
+      <c r="X39" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z39" s="5"/>
+      <c r="AA39" s="5"/>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P40" s="3" t="n">
+        <f aca="false">COS(3.14159265359/(Q40+1))</f>
+        <v>-1.03411553555107E-013</v>
+      </c>
+      <c r="Q40" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>0.4828</v>
+      </c>
+      <c r="S40" s="7" t="n">
+        <v>1.8094</v>
+      </c>
+      <c r="T40" s="7" t="n">
+        <v>1.8094</v>
+      </c>
+      <c r="U40" s="3" t="n">
+        <v>0.4828</v>
+      </c>
+      <c r="W40" s="3" t="n">
+        <f aca="false">COS(3.14159265359/(X40+1))</f>
+        <v>-1.03411553555107E-013</v>
+      </c>
+      <c r="X40" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y40" s="3" t="n">
+        <v>0.4828</v>
+      </c>
+      <c r="Z40" s="7" t="n">
+        <v>1.8094</v>
+      </c>
+      <c r="AA40" s="7" t="n">
+        <v>1.8094</v>
+      </c>
+      <c r="AB40" s="3" t="n">
+        <v>0.4828</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P41" s="3" t="n">
+        <f aca="false">COS(3.14159265359/(Q41+1))</f>
+        <v>0.49999999999994</v>
+      </c>
+      <c r="Q41" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="S41" s="3" t="n">
+        <v>1.824</v>
+      </c>
+      <c r="T41" s="3" t="n">
+        <v>1.8658</v>
+      </c>
+      <c r="U41" s="3" t="n">
+        <v>0.6327</v>
+      </c>
+      <c r="W41" s="3" t="n">
+        <f aca="false">COS(3.14159265359/(X41+1))</f>
+        <v>0.49999999999994</v>
+      </c>
+      <c r="X41" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y41" s="3" t="n">
+        <v>0.568</v>
+      </c>
+      <c r="Z41" s="7" t="n">
+        <v>1.8006</v>
+      </c>
+      <c r="AA41" s="7" t="n">
+        <v>1.8518</v>
+      </c>
+      <c r="AB41" s="3" t="n">
+        <v>0.6036</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P42" s="3" t="n">
+        <f aca="false">COS(3.14159265359/(Q42+1))</f>
+        <v>0.707106781186511</v>
+      </c>
+      <c r="Q42" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>0.7372</v>
+      </c>
+      <c r="S42" s="3" t="n">
+        <v>1.8354</v>
+      </c>
+      <c r="T42" s="3" t="n">
+        <v>1.8913</v>
+      </c>
+      <c r="U42" s="3" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="W42" s="3" t="n">
+        <f aca="false">COS(3.14159265359/(X42+1))</f>
+        <v>0.707106781186511</v>
+      </c>
+      <c r="X42" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y42" s="3" t="n">
+        <v>0.6827</v>
+      </c>
+      <c r="Z42" s="3" t="n">
+        <v>1.8071</v>
+      </c>
+      <c r="AA42" s="3" t="n">
+        <v>1.8727</v>
+      </c>
+      <c r="AB42" s="3" t="n">
+        <v>0.7165</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P43" s="3" t="n">
+        <f aca="false">COS(3.14159265359/(Q43+1))</f>
+        <v>0.809016994374923</v>
+      </c>
+      <c r="Q43" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="S43" s="3" t="n">
+        <v>1.8418</v>
+      </c>
+      <c r="T43" s="3" t="n">
+        <v>1.9051</v>
+      </c>
+      <c r="U43" s="3" t="n">
+        <v>0.8823</v>
+      </c>
+      <c r="W43" s="3" t="n">
+        <f aca="false">COS(3.14159265359/(X43+1))</f>
+        <v>0.809016994374923</v>
+      </c>
+      <c r="X43" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y43" s="3" t="n">
+        <v>0.7981</v>
+      </c>
+      <c r="Z43" s="3" t="n">
+        <v>1.8104</v>
+      </c>
+      <c r="AA43" s="3" t="n">
+        <v>1.8838</v>
+      </c>
+      <c r="AB43" s="3" t="n">
+        <v>0.8248</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="R44" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="S44" s="12" t="n">
+        <v>1.8469</v>
+      </c>
+      <c r="T44" s="12" t="n">
+        <v>1.9261</v>
+      </c>
+      <c r="U44" s="12" t="n">
+        <v>1.034</v>
+      </c>
+      <c r="Z44" s="12" t="n">
+        <v>1.8067</v>
+      </c>
+      <c r="AA44" s="12" t="n">
+        <v>1.8996</v>
+      </c>
+      <c r="AB44" s="12" t="n">
+        <v>1.074</v>
       </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Обычный"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Обычный"&amp;12Страница &amp;P</oddFooter>

--- a/exciton.xlsx
+++ b/exciton.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\ms_excitonic\"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="28">
   <si>
     <t>along N-Zn-N</t>
   </si>
@@ -118,7 +118,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -184,14 +184,14 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="1" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="1" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -282,10 +282,10 @@
   <a:themeElements>
     <a:clrScheme name="Стандартная">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -323,116 +323,52 @@
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
                 <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
                 <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
                 <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
                 <a:lumMod val="102000"/>
                 <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
                 <a:lumMod val="100000"/>
                 <a:shade val="100000"/>
               </a:schemeClr>
@@ -440,33 +376,24 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
                 <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
@@ -479,13 +406,7 @@
           <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -495,15 +416,13 @@
         <a:solidFill>
           <a:schemeClr val="phClr">
             <a:tint val="95000"/>
-            <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
               </a:schemeClr>
@@ -511,7 +430,6 @@
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
               </a:schemeClr>
@@ -519,22 +437,17 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="63000"/>
-                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
@@ -2929,7 +2842,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB44"/>
+  <dimension ref="A1:AB47"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.2">
@@ -3441,16 +3354,16 @@
       <c r="C16" s="3">
         <v>1</v>
       </c>
-      <c r="D16" s="12">
+      <c r="D16" s="11">
         <v>0.47199999999999998</v>
       </c>
-      <c r="E16" s="13">
+      <c r="E16" s="12">
         <v>1.8420000000000001</v>
       </c>
-      <c r="F16" s="13">
+      <c r="F16" s="12">
         <v>1.8420000000000001</v>
       </c>
-      <c r="G16" s="12">
+      <c r="G16" s="11">
         <v>0.47199999999999998</v>
       </c>
       <c r="P16" s="3">
@@ -3481,16 +3394,16 @@
       <c r="C17" s="3">
         <v>2</v>
       </c>
-      <c r="D17" s="14">
+      <c r="D17" s="13">
         <v>0.6845</v>
       </c>
-      <c r="E17" s="14">
+      <c r="E17" s="13">
         <v>1.7946</v>
       </c>
-      <c r="F17" s="14">
+      <c r="F17" s="13">
         <v>1.9097999999999999</v>
       </c>
-      <c r="G17" s="14">
+      <c r="G17" s="13">
         <v>0.66769999999999996</v>
       </c>
       <c r="P17" s="3">
@@ -3521,16 +3434,16 @@
       <c r="C18" s="3">
         <v>3</v>
       </c>
-      <c r="D18" s="14">
+      <c r="D18" s="13">
         <v>0.95720000000000005</v>
       </c>
-      <c r="E18" s="14">
+      <c r="E18" s="13">
         <v>1.7791999999999999</v>
       </c>
-      <c r="F18" s="14">
+      <c r="F18" s="13">
         <v>1.9390000000000001</v>
       </c>
-      <c r="G18" s="14">
+      <c r="G18" s="13">
         <v>0.82569999999999999</v>
       </c>
       <c r="P18" s="3">
@@ -3561,16 +3474,16 @@
       <c r="C19" s="3">
         <v>4</v>
       </c>
-      <c r="D19" s="14">
+      <c r="D19" s="13">
         <v>1.2312000000000001</v>
       </c>
-      <c r="E19" s="14">
+      <c r="E19" s="13">
         <v>1.7698</v>
       </c>
-      <c r="F19" s="14">
+      <c r="F19" s="13">
         <v>1.9551000000000001</v>
       </c>
-      <c r="G19" s="14">
+      <c r="G19" s="13">
         <v>0.9728</v>
       </c>
       <c r="P19" s="3">
@@ -3601,16 +3514,16 @@
       <c r="C20" s="3">
         <v>5</v>
       </c>
-      <c r="D20" s="12">
+      <c r="D20" s="11">
         <v>1.4281999999999999</v>
       </c>
-      <c r="E20" s="12">
+      <c r="E20" s="11">
         <v>1.7645</v>
       </c>
-      <c r="F20" s="12">
+      <c r="F20" s="11">
         <v>1.9653</v>
       </c>
-      <c r="G20" s="12">
+      <c r="G20" s="11">
         <v>1.1142000000000001</v>
       </c>
       <c r="R20" s="8">
@@ -3624,22 +3537,22 @@
       </c>
     </row>
     <row r="21" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="D21" s="15">
+      <c r="D21" s="14">
         <v>1.5469999999999999</v>
       </c>
-      <c r="E21" s="15">
+      <c r="E21" s="14">
         <v>1.7524</v>
       </c>
-      <c r="F21" s="15">
+      <c r="F21" s="14">
         <v>1.9819</v>
       </c>
-      <c r="G21" s="16">
+      <c r="G21" s="15">
         <v>1</v>
       </c>
       <c r="S21" s="9">
         <v>1.8030999999999999</v>
       </c>
-      <c r="T21" s="11">
+      <c r="T21" s="16">
         <v>1.9291</v>
       </c>
     </row>
@@ -3719,6 +3632,12 @@
       <c r="AA27" s="5"/>
     </row>
     <row r="28" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B28" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>1</v>
+      </c>
       <c r="P28" s="3">
         <f>COS(3.14159265359/(Q28+1))</f>
         <v>-1.0341152847231916E-13</v>
@@ -3726,16 +3645,16 @@
       <c r="Q28" s="3">
         <v>1</v>
       </c>
-      <c r="R28" s="12">
+      <c r="R28" s="11">
         <v>0.47199999999999998</v>
       </c>
-      <c r="S28" s="13">
+      <c r="S28" s="12">
         <v>1.8420000000000001</v>
       </c>
-      <c r="T28" s="13">
+      <c r="T28" s="12">
         <v>1.8420000000000001</v>
       </c>
-      <c r="U28" s="12">
+      <c r="U28" s="11">
         <v>0.47199999999999998</v>
       </c>
       <c r="W28" s="3">
@@ -3745,20 +3664,38 @@
       <c r="X28" s="3">
         <v>1</v>
       </c>
-      <c r="Y28" s="12">
+      <c r="Y28" s="11">
         <v>0.47199999999999998</v>
       </c>
-      <c r="Z28" s="13">
+      <c r="Z28" s="12">
         <v>1.8420000000000001</v>
       </c>
-      <c r="AA28" s="13">
+      <c r="AA28" s="12">
         <v>1.8420000000000001</v>
       </c>
-      <c r="AB28" s="12">
+      <c r="AB28" s="11">
         <v>0.47199999999999998</v>
       </c>
     </row>
     <row r="29" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B29" s="2">
+        <v>2</v>
+      </c>
+      <c r="C29" s="2">
+        <v>3.4</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>18</v>
+      </c>
       <c r="P29" s="3">
         <f>COS(3.14159265359/(Q29+1))</f>
         <v>0.49999999999994027</v>
@@ -3766,16 +3703,16 @@
       <c r="Q29" s="3">
         <v>2</v>
       </c>
-      <c r="R29" s="14">
+      <c r="R29" s="13">
         <v>0.56259999999999999</v>
       </c>
-      <c r="S29" s="14">
+      <c r="S29" s="13">
         <v>1.8226</v>
       </c>
-      <c r="T29" s="14">
+      <c r="T29" s="13">
         <v>1.9006000000000001</v>
       </c>
-      <c r="U29" s="14">
+      <c r="U29" s="13">
         <v>0.62329999999999997</v>
       </c>
       <c r="W29" s="3">
@@ -3785,20 +3722,25 @@
       <c r="X29" s="3">
         <v>2</v>
       </c>
-      <c r="Y29" s="14">
+      <c r="Y29" s="13">
         <v>0.52080000000000004</v>
       </c>
-      <c r="Z29" s="14">
+      <c r="Z29" s="13">
         <v>1.7909999999999999</v>
       </c>
-      <c r="AA29" s="14">
+      <c r="AA29" s="13">
         <v>1.8908</v>
       </c>
-      <c r="AB29" s="14">
+      <c r="AB29" s="13">
         <v>0.59809999999999997</v>
       </c>
     </row>
     <row r="30" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="C30" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="5"/>
+      <c r="F30" s="5"/>
       <c r="P30" s="3">
         <f>COS(3.14159265359/(Q30+1))</f>
         <v>0.70710678118651094</v>
@@ -3806,16 +3748,16 @@
       <c r="Q30" s="3">
         <v>3</v>
       </c>
-      <c r="R30" s="14">
+      <c r="R30" s="13">
         <v>0.6794</v>
       </c>
-      <c r="S30" s="14">
+      <c r="S30" s="13">
         <v>1.8207</v>
       </c>
-      <c r="T30" s="14">
+      <c r="T30" s="13">
         <v>1.9256</v>
       </c>
-      <c r="U30" s="14">
+      <c r="U30" s="13">
         <v>0.75419999999999998</v>
       </c>
       <c r="W30" s="3">
@@ -3825,20 +3767,39 @@
       <c r="X30" s="3">
         <v>3</v>
       </c>
-      <c r="Y30" s="14">
+      <c r="Y30" s="13">
         <v>0.61819999999999997</v>
       </c>
-      <c r="Z30" s="14">
+      <c r="Z30" s="13">
         <v>1.7823</v>
       </c>
-      <c r="AA30" s="14">
+      <c r="AA30" s="13">
         <v>1.9121999999999999</v>
       </c>
-      <c r="AB30" s="14">
+      <c r="AB30" s="13">
         <v>0.71540000000000004</v>
       </c>
     </row>
     <row r="31" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B31" s="3">
+        <f>COS(3.14159265359/(C31+1))</f>
+        <v>-1.0341152847231916E-13</v>
+      </c>
+      <c r="C31" s="3">
+        <v>1</v>
+      </c>
+      <c r="D31" s="11">
+        <v>0.47199999999999998</v>
+      </c>
+      <c r="E31" s="12">
+        <v>1.8420000000000001</v>
+      </c>
+      <c r="F31" s="12">
+        <v>1.8420000000000001</v>
+      </c>
+      <c r="G31" s="11">
+        <v>0.47199999999999998</v>
+      </c>
       <c r="P31" s="3">
         <f>COS(3.14159265359/(Q31+1))</f>
         <v>0.80901699437492314</v>
@@ -3846,16 +3807,16 @@
       <c r="Q31" s="3">
         <v>4</v>
       </c>
-      <c r="R31" s="14">
+      <c r="R31" s="13">
         <v>0.80520000000000003</v>
       </c>
-      <c r="S31" s="14">
+      <c r="S31" s="13">
         <v>1.82</v>
       </c>
-      <c r="T31" s="14">
+      <c r="T31" s="13">
         <v>1.9390000000000001</v>
       </c>
-      <c r="U31" s="14">
+      <c r="U31" s="13">
         <v>0.88119999999999998</v>
       </c>
       <c r="W31" s="3">
@@ -3865,51 +3826,129 @@
       <c r="X31" s="3">
         <v>4</v>
       </c>
-      <c r="Y31" s="14">
+      <c r="Y31" s="13">
         <v>0.73040000000000005</v>
       </c>
-      <c r="Z31" s="14">
+      <c r="Z31" s="13">
         <v>1.778</v>
       </c>
-      <c r="AA31" s="14">
+      <c r="AA31" s="13">
         <v>1.9235</v>
       </c>
-      <c r="AB31" s="14">
+      <c r="AB31" s="13">
         <v>0.82769999999999999</v>
       </c>
     </row>
     <row r="32" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="R32" s="18">
+      <c r="B32" s="3">
+        <f>COS(3.14159265359/(C32+1))</f>
+        <v>0.49999999999994027</v>
+      </c>
+      <c r="C32" s="3">
+        <v>2</v>
+      </c>
+      <c r="D32" s="13">
+        <v>0.68330000000000002</v>
+      </c>
+      <c r="E32" s="13">
+        <v>1.8963000000000001</v>
+      </c>
+      <c r="F32" s="13">
+        <v>1.8995</v>
+      </c>
+      <c r="G32" s="13">
+        <v>0.60629999999999995</v>
+      </c>
+      <c r="R32" s="17">
         <v>1</v>
       </c>
-      <c r="S32" s="15">
+      <c r="S32" s="14">
         <v>1.8123</v>
       </c>
-      <c r="T32" s="15">
+      <c r="T32" s="14">
         <v>1.9610000000000001</v>
       </c>
-      <c r="U32" s="15">
+      <c r="U32" s="14">
         <v>1.2170000000000001</v>
       </c>
-      <c r="Y32" s="18">
+      <c r="Y32" s="17">
         <v>1</v>
       </c>
-      <c r="Z32" s="17">
+      <c r="Z32" s="18">
         <v>1.7582</v>
       </c>
-      <c r="AA32" s="17">
+      <c r="AA32" s="18">
         <v>1.9418</v>
       </c>
-      <c r="AB32" s="17">
+      <c r="AB32" s="18">
         <v>1.357</v>
       </c>
     </row>
-    <row r="33" spans="16:28" x14ac:dyDescent="0.2">
-      <c r="S33" s="9"/>
-      <c r="T33" s="9"/>
-      <c r="U33" s="9"/>
-    </row>
-    <row r="37" spans="16:28" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B33" s="3">
+        <f>COS(3.14159265359/(C33+1))</f>
+        <v>0.70710678118651094</v>
+      </c>
+      <c r="C33" s="3">
+        <v>3</v>
+      </c>
+      <c r="D33" s="13">
+        <v>0.87429999999999997</v>
+      </c>
+      <c r="E33" s="13">
+        <v>1.9197</v>
+      </c>
+      <c r="F33" s="13">
+        <v>1.9226000000000001</v>
+      </c>
+      <c r="G33" s="13">
+        <v>0.70530000000000004</v>
+      </c>
+      <c r="S33" s="3"/>
+      <c r="T33" s="3"/>
+      <c r="U33" s="3"/>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B34" s="3">
+        <f>COS(3.14159265359/(C34+1))</f>
+        <v>0.80901699437492314</v>
+      </c>
+      <c r="C34" s="3">
+        <v>4</v>
+      </c>
+      <c r="D34" s="13">
+        <v>1.0605</v>
+      </c>
+      <c r="E34" s="13">
+        <v>1.9320999999999999</v>
+      </c>
+      <c r="F34" s="13">
+        <v>1.9347000000000001</v>
+      </c>
+      <c r="G34" s="13">
+        <v>0.79759999999999998</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="D35" s="18">
+        <v>1.819</v>
+      </c>
+      <c r="E35" s="14">
+        <v>1.9524999999999999</v>
+      </c>
+      <c r="F35" s="14">
+        <v>1.9563999999999999</v>
+      </c>
+      <c r="G35" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="P37" s="3" t="s">
         <v>9</v>
       </c>
@@ -3923,7 +3962,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="16:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="P38" s="10">
         <v>1.75</v>
       </c>
@@ -3961,7 +4000,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="39" spans="16:28" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="Q39" s="3" t="s">
         <v>19</v>
       </c>
@@ -3973,7 +4012,13 @@
       <c r="Z39" s="5"/>
       <c r="AA39" s="5"/>
     </row>
-    <row r="40" spans="16:28" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B40" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>1</v>
+      </c>
       <c r="P40" s="3">
         <f>COS(3.14159265359/(Q40+1))</f>
         <v>-1.0341152847231916E-13</v>
@@ -3981,16 +4026,16 @@
       <c r="Q40" s="3">
         <v>1</v>
       </c>
-      <c r="R40" s="12">
+      <c r="R40" s="11">
         <v>0.47199999999999998</v>
       </c>
-      <c r="S40" s="13">
+      <c r="S40" s="12">
         <v>1.8420000000000001</v>
       </c>
-      <c r="T40" s="13">
+      <c r="T40" s="12">
         <v>1.8420000000000001</v>
       </c>
-      <c r="U40" s="12">
+      <c r="U40" s="11">
         <v>0.47199999999999998</v>
       </c>
       <c r="W40" s="3">
@@ -4000,20 +4045,38 @@
       <c r="X40" s="3">
         <v>1</v>
       </c>
-      <c r="Y40" s="12">
+      <c r="Y40" s="11">
         <v>0.47199999999999998</v>
       </c>
-      <c r="Z40" s="13">
+      <c r="Z40" s="12">
         <v>1.8420000000000001</v>
       </c>
-      <c r="AA40" s="13">
+      <c r="AA40" s="12">
         <v>1.8420000000000001</v>
       </c>
-      <c r="AB40" s="12">
+      <c r="AB40" s="11">
         <v>0.47199999999999998</v>
       </c>
     </row>
-    <row r="41" spans="16:28" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B41" s="10">
+        <v>1.75</v>
+      </c>
+      <c r="C41" s="2">
+        <v>3.4</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>18</v>
+      </c>
       <c r="P41" s="3">
         <f>COS(3.14159265359/(Q41+1))</f>
         <v>0.49999999999994027</v>
@@ -4021,16 +4084,16 @@
       <c r="Q41" s="3">
         <v>2</v>
       </c>
-      <c r="R41" s="14">
+      <c r="R41" s="13">
         <v>0.56810000000000005</v>
       </c>
-      <c r="S41" s="14">
+      <c r="S41" s="13">
         <v>1.8462000000000001</v>
       </c>
-      <c r="T41" s="14">
+      <c r="T41" s="13">
         <v>1.8887</v>
       </c>
-      <c r="U41" s="14">
+      <c r="U41" s="13">
         <v>0.59860000000000002</v>
       </c>
       <c r="W41" s="3">
@@ -4040,20 +4103,25 @@
       <c r="X41" s="3">
         <v>2</v>
       </c>
-      <c r="Y41" s="14">
+      <c r="Y41" s="13">
         <v>0.5242</v>
       </c>
-      <c r="Z41" s="14">
+      <c r="Z41" s="13">
         <v>1.8202</v>
       </c>
-      <c r="AA41" s="14">
+      <c r="AA41" s="13">
         <v>1.8723000000000001</v>
       </c>
-      <c r="AB41" s="14">
+      <c r="AB41" s="13">
         <v>0.56389999999999996</v>
       </c>
     </row>
-    <row r="42" spans="16:28" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="C42" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E42" s="5"/>
+      <c r="F42" s="5"/>
       <c r="P42" s="3">
         <f>COS(3.14159265359/(Q42+1))</f>
         <v>0.70710678118651094</v>
@@ -4061,16 +4129,16 @@
       <c r="Q42" s="3">
         <v>3</v>
       </c>
-      <c r="R42" s="14">
+      <c r="R42" s="13">
         <v>0.68169999999999997</v>
       </c>
-      <c r="S42" s="14">
+      <c r="S42" s="13">
         <v>1.8543000000000001</v>
       </c>
-      <c r="T42" s="14">
+      <c r="T42" s="13">
         <v>1.91</v>
       </c>
-      <c r="U42" s="14">
+      <c r="U42" s="13">
         <v>0.71209999999999996</v>
       </c>
       <c r="W42" s="3">
@@ -4080,20 +4148,39 @@
       <c r="X42" s="3">
         <v>3</v>
       </c>
-      <c r="Y42" s="14">
+      <c r="Y42" s="13">
         <v>0.62319999999999998</v>
       </c>
-      <c r="Z42" s="14">
+      <c r="Z42" s="13">
         <v>1.8237000000000001</v>
       </c>
-      <c r="AA42" s="14">
+      <c r="AA42" s="13">
         <v>1.8889</v>
       </c>
-      <c r="AB42" s="14">
+      <c r="AB42" s="13">
         <v>0.66220000000000001</v>
       </c>
     </row>
-    <row r="43" spans="16:28" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B43" s="3">
+        <f>COS(3.14159265359/(C43+1))</f>
+        <v>-1.0341152847231916E-13</v>
+      </c>
+      <c r="C43" s="3">
+        <v>1</v>
+      </c>
+      <c r="D43" s="11">
+        <v>0.47199999999999998</v>
+      </c>
+      <c r="E43" s="12">
+        <v>1.8420000000000001</v>
+      </c>
+      <c r="F43" s="12">
+        <v>1.8420000000000001</v>
+      </c>
+      <c r="G43" s="11">
+        <v>0.47199999999999998</v>
+      </c>
       <c r="P43" s="3">
         <f>COS(3.14159265359/(Q43+1))</f>
         <v>0.80901699437492314</v>
@@ -4101,16 +4188,16 @@
       <c r="Q43" s="3">
         <v>4</v>
       </c>
-      <c r="R43" s="14">
+      <c r="R43" s="13">
         <v>0.7954</v>
       </c>
-      <c r="S43" s="14">
+      <c r="S43" s="13">
         <v>1.8586</v>
       </c>
-      <c r="T43" s="14">
+      <c r="T43" s="13">
         <v>1.9213</v>
       </c>
-      <c r="U43" s="14">
+      <c r="U43" s="13">
         <v>0.8206</v>
       </c>
       <c r="W43" s="3">
@@ -4120,43 +4207,118 @@
       <c r="X43" s="3">
         <v>4</v>
       </c>
-      <c r="Y43" s="14">
+      <c r="Y43" s="13">
         <v>0.72309999999999997</v>
       </c>
-      <c r="Z43" s="14">
+      <c r="Z43" s="13">
         <v>1.8249</v>
       </c>
-      <c r="AA43" s="14">
+      <c r="AA43" s="13">
         <v>1.8973</v>
       </c>
-      <c r="AB43" s="14">
+      <c r="AB43" s="13">
         <v>0.75609999999999999</v>
       </c>
     </row>
-    <row r="44" spans="16:28" x14ac:dyDescent="0.2">
-      <c r="R44" s="18">
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B44" s="3">
+        <f>COS(3.14159265359/(C44+1))</f>
+        <v>0.49999999999994027</v>
+      </c>
+      <c r="C44" s="3">
+        <v>2</v>
+      </c>
+      <c r="D44" s="13">
+        <v>0.68330000000000002</v>
+      </c>
+      <c r="E44" s="13">
+        <v>1.8963000000000001</v>
+      </c>
+      <c r="F44" s="13">
+        <v>1.8995</v>
+      </c>
+      <c r="G44" s="13">
+        <v>0.60629999999999995</v>
+      </c>
+      <c r="R44" s="17">
         <v>1</v>
       </c>
-      <c r="S44" s="17">
+      <c r="S44" s="18">
         <v>1.8599000000000001</v>
       </c>
-      <c r="T44" s="17">
+      <c r="T44" s="18">
         <v>1.9388000000000001</v>
       </c>
-      <c r="U44" s="17">
+      <c r="U44" s="18">
         <v>1.07</v>
       </c>
-      <c r="Y44" s="17">
+      <c r="Y44" s="18">
         <v>1</v>
       </c>
-      <c r="Z44" s="17">
+      <c r="Z44" s="18">
         <v>1.8164</v>
       </c>
-      <c r="AA44" s="17">
+      <c r="AA44" s="18">
         <v>1.9087000000000001</v>
       </c>
-      <c r="AB44" s="17">
+      <c r="AB44" s="18">
         <v>1.115</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B45" s="3">
+        <f>COS(3.14159265359/(C45+1))</f>
+        <v>0.70710678118651094</v>
+      </c>
+      <c r="C45" s="3">
+        <v>3</v>
+      </c>
+      <c r="D45" s="13">
+        <v>0.85880000000000001</v>
+      </c>
+      <c r="E45" s="13">
+        <v>1.9279999999999999</v>
+      </c>
+      <c r="F45" s="13">
+        <v>1.9297</v>
+      </c>
+      <c r="G45" s="13">
+        <v>0.70550000000000002</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="B46" s="3">
+        <f>COS(3.14159265359/(C46+1))</f>
+        <v>0.80901699437492314</v>
+      </c>
+      <c r="C46" s="3">
+        <v>4</v>
+      </c>
+      <c r="D46" s="13">
+        <v>1.0357000000000001</v>
+      </c>
+      <c r="E46" s="13">
+        <v>1.9426000000000001</v>
+      </c>
+      <c r="F46" s="13">
+        <v>1.9429000000000001</v>
+      </c>
+      <c r="G46" s="13">
+        <v>0.78949999999999998</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="D47" s="18">
+        <v>1.7749999999999999</v>
+      </c>
+      <c r="E47" s="18">
+        <v>1.9630000000000001</v>
+      </c>
+      <c r="F47" s="18">
+        <v>1.9650000000000001</v>
+      </c>
+      <c r="G47" s="17">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
